--- a/output/version3/test/15-10/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>670</v>
+        <v>487</v>
       </c>
       <c r="C2" t="n">
-        <v>644</v>
+        <v>624</v>
       </c>
       <c r="D2" t="n">
-        <v>639</v>
+        <v>624</v>
       </c>
       <c r="E2" t="n">
-        <v>667</v>
+        <v>566</v>
       </c>
       <c r="F2" t="n">
-        <v>569</v>
+        <v>656</v>
       </c>
       <c r="G2" t="n">
-        <v>682</v>
+        <v>601</v>
       </c>
       <c r="H2" t="n">
+        <v>649</v>
+      </c>
+      <c r="I2" t="n">
+        <v>694</v>
+      </c>
+      <c r="J2" t="n">
         <v>565</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>734</v>
       </c>
-      <c r="J2" t="n">
-        <v>658</v>
-      </c>
-      <c r="K2" t="n">
-        <v>661</v>
-      </c>
       <c r="L2" t="n">
-        <v>648.9</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>572</v>
+        <v>648</v>
       </c>
       <c r="C3" t="n">
-        <v>587</v>
+        <v>741</v>
       </c>
       <c r="D3" t="n">
-        <v>597</v>
+        <v>666</v>
       </c>
       <c r="E3" t="n">
-        <v>635</v>
+        <v>664</v>
       </c>
       <c r="F3" t="n">
-        <v>684</v>
+        <v>598</v>
       </c>
       <c r="G3" t="n">
-        <v>519</v>
+        <v>623</v>
       </c>
       <c r="H3" t="n">
-        <v>612</v>
+        <v>774</v>
       </c>
       <c r="I3" t="n">
-        <v>671</v>
+        <v>542</v>
       </c>
       <c r="J3" t="n">
-        <v>760</v>
+        <v>618</v>
       </c>
       <c r="K3" t="n">
-        <v>618</v>
+        <v>570</v>
       </c>
       <c r="L3" t="n">
-        <v>625.5</v>
+        <v>644.4</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>727</v>
+        <v>645</v>
       </c>
       <c r="C4" t="n">
-        <v>608</v>
+        <v>689</v>
       </c>
       <c r="D4" t="n">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="E4" t="n">
-        <v>698</v>
+        <v>613</v>
       </c>
       <c r="F4" t="n">
-        <v>694</v>
+        <v>603</v>
       </c>
       <c r="G4" t="n">
-        <v>760</v>
+        <v>553</v>
       </c>
       <c r="H4" t="n">
-        <v>687</v>
+        <v>599</v>
       </c>
       <c r="I4" t="n">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="J4" t="n">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="K4" t="n">
-        <v>560</v>
+        <v>635</v>
       </c>
       <c r="L4" t="n">
-        <v>665.7</v>
+        <v>629.6</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>810</v>
+        <v>728</v>
       </c>
       <c r="C5" t="n">
-        <v>739</v>
+        <v>686</v>
       </c>
       <c r="D5" t="n">
-        <v>747</v>
+        <v>722</v>
       </c>
       <c r="E5" t="n">
-        <v>638</v>
+        <v>721</v>
       </c>
       <c r="F5" t="n">
-        <v>727</v>
+        <v>573</v>
       </c>
       <c r="G5" t="n">
-        <v>670</v>
+        <v>759</v>
       </c>
       <c r="H5" t="n">
-        <v>705</v>
+        <v>741</v>
       </c>
       <c r="I5" t="n">
-        <v>762</v>
+        <v>659</v>
       </c>
       <c r="J5" t="n">
-        <v>647</v>
+        <v>703</v>
       </c>
       <c r="K5" t="n">
-        <v>732</v>
+        <v>657</v>
       </c>
       <c r="L5" t="n">
-        <v>717.7</v>
+        <v>694.9</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>624</v>
+        <v>653</v>
       </c>
       <c r="C6" t="n">
-        <v>582</v>
+        <v>676</v>
       </c>
       <c r="D6" t="n">
-        <v>634</v>
+        <v>574</v>
       </c>
       <c r="E6" t="n">
-        <v>705</v>
+        <v>610</v>
       </c>
       <c r="F6" t="n">
-        <v>589</v>
+        <v>686</v>
       </c>
       <c r="G6" t="n">
-        <v>703</v>
+        <v>577</v>
       </c>
       <c r="H6" t="n">
-        <v>579</v>
+        <v>658</v>
       </c>
       <c r="I6" t="n">
-        <v>649</v>
+        <v>608</v>
       </c>
       <c r="J6" t="n">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="K6" t="n">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="L6" t="n">
-        <v>634.5</v>
+        <v>633.8</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>677</v>
+        <v>646</v>
       </c>
       <c r="C7" t="n">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D7" t="n">
+        <v>617</v>
+      </c>
+      <c r="E7" t="n">
+        <v>622</v>
+      </c>
+      <c r="F7" t="n">
         <v>643</v>
       </c>
-      <c r="E7" t="n">
-        <v>766</v>
-      </c>
-      <c r="F7" t="n">
-        <v>559</v>
-      </c>
       <c r="G7" t="n">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="H7" t="n">
-        <v>599</v>
+        <v>631</v>
       </c>
       <c r="I7" t="n">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="J7" t="n">
-        <v>695</v>
+        <v>651</v>
       </c>
       <c r="K7" t="n">
-        <v>701</v>
+        <v>543</v>
       </c>
       <c r="L7" t="n">
-        <v>659</v>
+        <v>633.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>636</v>
+        <v>682</v>
       </c>
       <c r="C8" t="n">
-        <v>633</v>
+        <v>607</v>
       </c>
       <c r="D8" t="n">
-        <v>624</v>
+        <v>656</v>
       </c>
       <c r="E8" t="n">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F8" t="n">
-        <v>676</v>
+        <v>744</v>
       </c>
       <c r="G8" t="n">
-        <v>604</v>
+        <v>564</v>
       </c>
       <c r="H8" t="n">
-        <v>656</v>
+        <v>717</v>
       </c>
       <c r="I8" t="n">
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="J8" t="n">
-        <v>708</v>
+        <v>568</v>
       </c>
       <c r="K8" t="n">
-        <v>546</v>
+        <v>741</v>
       </c>
       <c r="L8" t="n">
-        <v>635.5</v>
+        <v>653.4</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>642</v>
+        <v>603</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>637</v>
       </c>
       <c r="D9" t="n">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="E9" t="n">
-        <v>552</v>
+        <v>671</v>
       </c>
       <c r="F9" t="n">
-        <v>598</v>
+        <v>746</v>
       </c>
       <c r="G9" t="n">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="H9" t="n">
-        <v>586</v>
+        <v>671</v>
       </c>
       <c r="I9" t="n">
-        <v>641</v>
+        <v>676</v>
       </c>
       <c r="J9" t="n">
+        <v>636</v>
+      </c>
+      <c r="K9" t="n">
         <v>630</v>
       </c>
-      <c r="K9" t="n">
-        <v>633</v>
-      </c>
       <c r="L9" t="n">
-        <v>606.1</v>
+        <v>649.2</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>698</v>
+        <v>798</v>
       </c>
       <c r="C10" t="n">
-        <v>735</v>
+        <v>858</v>
       </c>
       <c r="D10" t="n">
-        <v>701</v>
+        <v>796</v>
       </c>
       <c r="E10" t="n">
-        <v>780</v>
+        <v>692</v>
       </c>
       <c r="F10" t="n">
-        <v>818</v>
+        <v>641</v>
       </c>
       <c r="G10" t="n">
-        <v>799</v>
+        <v>760</v>
       </c>
       <c r="H10" t="n">
-        <v>698</v>
+        <v>867</v>
       </c>
       <c r="I10" t="n">
-        <v>725</v>
+        <v>768</v>
       </c>
       <c r="J10" t="n">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="K10" t="n">
-        <v>725</v>
+        <v>827</v>
       </c>
       <c r="L10" t="n">
-        <v>737.6</v>
+        <v>769.1</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>628</v>
+        <v>668</v>
       </c>
       <c r="C11" t="n">
-        <v>627</v>
+        <v>788</v>
       </c>
       <c r="D11" t="n">
+        <v>654</v>
+      </c>
+      <c r="E11" t="n">
+        <v>601</v>
+      </c>
+      <c r="F11" t="n">
+        <v>662</v>
+      </c>
+      <c r="G11" t="n">
+        <v>650</v>
+      </c>
+      <c r="H11" t="n">
+        <v>726</v>
+      </c>
+      <c r="I11" t="n">
         <v>646</v>
       </c>
-      <c r="E11" t="n">
-        <v>687</v>
-      </c>
-      <c r="F11" t="n">
-        <v>550</v>
-      </c>
-      <c r="G11" t="n">
-        <v>653</v>
-      </c>
-      <c r="H11" t="n">
-        <v>651</v>
-      </c>
-      <c r="I11" t="n">
-        <v>699</v>
-      </c>
       <c r="J11" t="n">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="K11" t="n">
-        <v>694</v>
+        <v>631</v>
       </c>
       <c r="L11" t="n">
-        <v>650.7</v>
+        <v>668</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>638</v>
+        <v>661</v>
       </c>
       <c r="C12" t="n">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="D12" t="n">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="E12" t="n">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="F12" t="n">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="G12" t="n">
-        <v>676</v>
+        <v>653</v>
       </c>
       <c r="H12" t="n">
-        <v>718</v>
+        <v>657</v>
       </c>
       <c r="I12" t="n">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="J12" t="n">
-        <v>685</v>
+        <v>646</v>
       </c>
       <c r="K12" t="n">
-        <v>630</v>
+        <v>657</v>
       </c>
       <c r="L12" t="n">
-        <v>669.7</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>865</v>
+        <v>741</v>
       </c>
       <c r="C13" t="n">
-        <v>824</v>
+        <v>681</v>
       </c>
       <c r="D13" t="n">
-        <v>712</v>
+        <v>830</v>
       </c>
       <c r="E13" t="n">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="F13" t="n">
-        <v>724</v>
+        <v>654</v>
       </c>
       <c r="G13" t="n">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="H13" t="n">
-        <v>717</v>
+        <v>667</v>
       </c>
       <c r="I13" t="n">
-        <v>854</v>
+        <v>782</v>
       </c>
       <c r="J13" t="n">
-        <v>692</v>
+        <v>793</v>
       </c>
       <c r="K13" t="n">
-        <v>764</v>
+        <v>667</v>
       </c>
       <c r="L13" t="n">
-        <v>772.7</v>
+        <v>737.1</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>680</v>
+        <v>789</v>
       </c>
       <c r="C14" t="n">
-        <v>722</v>
+        <v>685</v>
       </c>
       <c r="D14" t="n">
         <v>747</v>
       </c>
       <c r="E14" t="n">
-        <v>771</v>
+        <v>639</v>
       </c>
       <c r="F14" t="n">
-        <v>661</v>
+        <v>722</v>
       </c>
       <c r="G14" t="n">
-        <v>690</v>
+        <v>791</v>
       </c>
       <c r="H14" t="n">
-        <v>802</v>
+        <v>821</v>
       </c>
       <c r="I14" t="n">
-        <v>641</v>
+        <v>714</v>
       </c>
       <c r="J14" t="n">
-        <v>879</v>
+        <v>694</v>
       </c>
       <c r="K14" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L14" t="n">
-        <v>729.1</v>
+        <v>730.6</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>695</v>
+        <v>786</v>
       </c>
       <c r="C15" t="n">
-        <v>663</v>
+        <v>723</v>
       </c>
       <c r="D15" t="n">
-        <v>724</v>
+        <v>657</v>
       </c>
       <c r="E15" t="n">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="F15" t="n">
-        <v>738</v>
+        <v>700</v>
       </c>
       <c r="G15" t="n">
+        <v>745</v>
+      </c>
+      <c r="H15" t="n">
         <v>641</v>
       </c>
-      <c r="H15" t="n">
-        <v>676</v>
-      </c>
       <c r="I15" t="n">
-        <v>768</v>
+        <v>698</v>
       </c>
       <c r="J15" t="n">
-        <v>744</v>
+        <v>703</v>
       </c>
       <c r="K15" t="n">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="L15" t="n">
-        <v>700.6</v>
+        <v>701.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>655</v>
+        <v>732</v>
       </c>
       <c r="C16" t="n">
-        <v>659</v>
+        <v>612</v>
       </c>
       <c r="D16" t="n">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="E16" t="n">
-        <v>672</v>
+        <v>737</v>
       </c>
       <c r="F16" t="n">
-        <v>804</v>
+        <v>730</v>
       </c>
       <c r="G16" t="n">
-        <v>736</v>
+        <v>611</v>
       </c>
       <c r="H16" t="n">
-        <v>666</v>
+        <v>641</v>
       </c>
       <c r="I16" t="n">
-        <v>681</v>
+        <v>617</v>
       </c>
       <c r="J16" t="n">
-        <v>733</v>
+        <v>682</v>
       </c>
       <c r="K16" t="n">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="L16" t="n">
-        <v>701.7</v>
+        <v>673.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>569</v>
+        <v>672</v>
       </c>
       <c r="C17" t="n">
-        <v>596</v>
+        <v>715</v>
       </c>
       <c r="D17" t="n">
-        <v>664</v>
+        <v>558</v>
       </c>
       <c r="E17" t="n">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F17" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="G17" t="n">
-        <v>633</v>
+        <v>715</v>
       </c>
       <c r="H17" t="n">
-        <v>648</v>
+        <v>598</v>
       </c>
       <c r="I17" t="n">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="J17" t="n">
-        <v>709</v>
+        <v>651</v>
       </c>
       <c r="K17" t="n">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="L17" t="n">
-        <v>642.8</v>
+        <v>651.9</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>766</v>
+        <v>690</v>
       </c>
       <c r="C18" t="n">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D18" t="n">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="E18" t="n">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="F18" t="n">
-        <v>744</v>
+        <v>673</v>
       </c>
       <c r="G18" t="n">
-        <v>733</v>
+        <v>680</v>
       </c>
       <c r="H18" t="n">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="I18" t="n">
-        <v>748</v>
+        <v>700</v>
       </c>
       <c r="J18" t="n">
-        <v>609</v>
+        <v>590</v>
       </c>
       <c r="K18" t="n">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="L18" t="n">
-        <v>700.3</v>
+        <v>676</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>657</v>
+        <v>738</v>
       </c>
       <c r="C19" t="n">
+        <v>673</v>
+      </c>
+      <c r="D19" t="n">
+        <v>614</v>
+      </c>
+      <c r="E19" t="n">
+        <v>669</v>
+      </c>
+      <c r="F19" t="n">
+        <v>640</v>
+      </c>
+      <c r="G19" t="n">
+        <v>653</v>
+      </c>
+      <c r="H19" t="n">
+        <v>689</v>
+      </c>
+      <c r="I19" t="n">
+        <v>686</v>
+      </c>
+      <c r="J19" t="n">
         <v>723</v>
       </c>
-      <c r="D19" t="n">
-        <v>672</v>
-      </c>
-      <c r="E19" t="n">
-        <v>680</v>
-      </c>
-      <c r="F19" t="n">
-        <v>766</v>
-      </c>
-      <c r="G19" t="n">
-        <v>613</v>
-      </c>
-      <c r="H19" t="n">
-        <v>778</v>
-      </c>
-      <c r="I19" t="n">
-        <v>670</v>
-      </c>
-      <c r="J19" t="n">
-        <v>705</v>
-      </c>
       <c r="K19" t="n">
-        <v>729</v>
+        <v>617</v>
       </c>
       <c r="L19" t="n">
-        <v>699.3</v>
+        <v>670.2</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>791</v>
+        <v>847</v>
       </c>
       <c r="C20" t="n">
-        <v>717</v>
+        <v>801</v>
       </c>
       <c r="D20" t="n">
-        <v>711</v>
+        <v>800</v>
       </c>
       <c r="E20" t="n">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="F20" t="n">
-        <v>692</v>
+        <v>760</v>
       </c>
       <c r="G20" t="n">
-        <v>717</v>
+        <v>757</v>
       </c>
       <c r="H20" t="n">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="I20" t="n">
-        <v>783</v>
+        <v>732</v>
       </c>
       <c r="J20" t="n">
-        <v>737</v>
+        <v>669</v>
       </c>
       <c r="K20" t="n">
-        <v>729</v>
+        <v>801</v>
       </c>
       <c r="L20" t="n">
-        <v>752.1</v>
+        <v>781.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>833</v>
+        <v>799</v>
       </c>
       <c r="C21" t="n">
-        <v>700</v>
+        <v>860</v>
       </c>
       <c r="D21" t="n">
-        <v>759</v>
+        <v>685</v>
       </c>
       <c r="E21" t="n">
-        <v>788</v>
+        <v>713</v>
       </c>
       <c r="F21" t="n">
-        <v>632</v>
+        <v>758</v>
       </c>
       <c r="G21" t="n">
-        <v>849</v>
+        <v>701</v>
       </c>
       <c r="H21" t="n">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="I21" t="n">
-        <v>704</v>
+        <v>737</v>
       </c>
       <c r="J21" t="n">
-        <v>753</v>
+        <v>848</v>
       </c>
       <c r="K21" t="n">
-        <v>888</v>
+        <v>697</v>
       </c>
       <c r="L21" t="n">
-        <v>775.6</v>
+        <v>765.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
+        <v>673</v>
+      </c>
+      <c r="C22" t="n">
+        <v>693</v>
+      </c>
+      <c r="D22" t="n">
+        <v>738</v>
+      </c>
+      <c r="E22" t="n">
+        <v>656</v>
+      </c>
+      <c r="F22" t="n">
+        <v>727</v>
+      </c>
+      <c r="G22" t="n">
+        <v>728</v>
+      </c>
+      <c r="H22" t="n">
+        <v>574</v>
+      </c>
+      <c r="I22" t="n">
+        <v>707</v>
+      </c>
+      <c r="J22" t="n">
+        <v>620</v>
+      </c>
+      <c r="K22" t="n">
         <v>676</v>
       </c>
-      <c r="C22" t="n">
-        <v>780</v>
-      </c>
-      <c r="D22" t="n">
-        <v>692</v>
-      </c>
-      <c r="E22" t="n">
-        <v>592</v>
-      </c>
-      <c r="F22" t="n">
-        <v>633</v>
-      </c>
-      <c r="G22" t="n">
-        <v>660</v>
-      </c>
-      <c r="H22" t="n">
-        <v>622</v>
-      </c>
-      <c r="I22" t="n">
-        <v>691</v>
-      </c>
-      <c r="J22" t="n">
-        <v>695</v>
-      </c>
-      <c r="K22" t="n">
-        <v>706</v>
-      </c>
       <c r="L22" t="n">
-        <v>674.7</v>
+        <v>679.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>723</v>
+        <v>628</v>
       </c>
       <c r="C23" t="n">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="D23" t="n">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="E23" t="n">
-        <v>720</v>
+        <v>643</v>
       </c>
       <c r="F23" t="n">
-        <v>704</v>
+        <v>627</v>
       </c>
       <c r="G23" t="n">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="H23" t="n">
-        <v>576</v>
+        <v>709</v>
       </c>
       <c r="I23" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="J23" t="n">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="K23" t="n">
-        <v>613</v>
+        <v>677</v>
       </c>
       <c r="L23" t="n">
-        <v>658</v>
+        <v>650.8</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="C24" t="n">
-        <v>732</v>
+        <v>676</v>
       </c>
       <c r="D24" t="n">
-        <v>895</v>
+        <v>795</v>
       </c>
       <c r="E24" t="n">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="F24" t="n">
-        <v>688</v>
+        <v>804</v>
       </c>
       <c r="G24" t="n">
-        <v>750</v>
+        <v>803</v>
       </c>
       <c r="H24" t="n">
-        <v>771</v>
+        <v>734</v>
       </c>
       <c r="I24" t="n">
-        <v>754</v>
+        <v>695</v>
       </c>
       <c r="J24" t="n">
-        <v>680</v>
+        <v>728</v>
       </c>
       <c r="K24" t="n">
-        <v>715</v>
+        <v>752</v>
       </c>
       <c r="L24" t="n">
-        <v>732.7</v>
+        <v>736.6</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
+        <v>626</v>
+      </c>
+      <c r="C25" t="n">
+        <v>660</v>
+      </c>
+      <c r="D25" t="n">
+        <v>686</v>
+      </c>
+      <c r="E25" t="n">
+        <v>703</v>
+      </c>
+      <c r="F25" t="n">
+        <v>671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>746</v>
+      </c>
+      <c r="H25" t="n">
+        <v>627</v>
+      </c>
+      <c r="I25" t="n">
+        <v>642</v>
+      </c>
+      <c r="J25" t="n">
+        <v>567</v>
+      </c>
+      <c r="K25" t="n">
         <v>704</v>
       </c>
-      <c r="C25" t="n">
-        <v>696</v>
-      </c>
-      <c r="D25" t="n">
-        <v>677</v>
-      </c>
-      <c r="E25" t="n">
-        <v>688</v>
-      </c>
-      <c r="F25" t="n">
-        <v>611</v>
-      </c>
-      <c r="G25" t="n">
-        <v>724</v>
-      </c>
-      <c r="H25" t="n">
-        <v>614</v>
-      </c>
-      <c r="I25" t="n">
-        <v>554</v>
-      </c>
-      <c r="J25" t="n">
-        <v>676</v>
-      </c>
-      <c r="K25" t="n">
-        <v>742</v>
-      </c>
       <c r="L25" t="n">
-        <v>668.6</v>
+        <v>663.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>654</v>
+        <v>741</v>
       </c>
       <c r="C26" t="n">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="D26" t="n">
-        <v>686</v>
+        <v>611</v>
       </c>
       <c r="E26" t="n">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="F26" t="n">
-        <v>825</v>
+        <v>776</v>
       </c>
       <c r="G26" t="n">
-        <v>666</v>
+        <v>633</v>
       </c>
       <c r="H26" t="n">
-        <v>789</v>
+        <v>668</v>
       </c>
       <c r="I26" t="n">
-        <v>562</v>
+        <v>699</v>
       </c>
       <c r="J26" t="n">
-        <v>645</v>
+        <v>697</v>
       </c>
       <c r="K26" t="n">
-        <v>718</v>
+        <v>656</v>
       </c>
       <c r="L26" t="n">
-        <v>701.6</v>
+        <v>696</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
+        <v>647</v>
+      </c>
+      <c r="C27" t="n">
+        <v>596</v>
+      </c>
+      <c r="D27" t="n">
+        <v>664</v>
+      </c>
+      <c r="E27" t="n">
+        <v>602</v>
+      </c>
+      <c r="F27" t="n">
+        <v>561</v>
+      </c>
+      <c r="G27" t="n">
+        <v>652</v>
+      </c>
+      <c r="H27" t="n">
+        <v>584</v>
+      </c>
+      <c r="I27" t="n">
+        <v>722</v>
+      </c>
+      <c r="J27" t="n">
+        <v>742</v>
+      </c>
+      <c r="K27" t="n">
         <v>683</v>
       </c>
-      <c r="C27" t="n">
-        <v>615</v>
-      </c>
-      <c r="D27" t="n">
-        <v>747</v>
-      </c>
-      <c r="E27" t="n">
-        <v>690</v>
-      </c>
-      <c r="F27" t="n">
-        <v>557</v>
-      </c>
-      <c r="G27" t="n">
-        <v>613</v>
-      </c>
-      <c r="H27" t="n">
-        <v>663</v>
-      </c>
-      <c r="I27" t="n">
-        <v>596</v>
-      </c>
-      <c r="J27" t="n">
-        <v>723</v>
-      </c>
-      <c r="K27" t="n">
-        <v>712</v>
-      </c>
       <c r="L27" t="n">
-        <v>659.9</v>
+        <v>645.3</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>636</v>
+        <v>671</v>
       </c>
       <c r="C28" t="n">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="D28" t="n">
-        <v>635</v>
+        <v>657</v>
       </c>
       <c r="E28" t="n">
-        <v>639</v>
+        <v>690</v>
       </c>
       <c r="F28" t="n">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="G28" t="n">
-        <v>629</v>
+        <v>579</v>
       </c>
       <c r="H28" t="n">
-        <v>664</v>
+        <v>640</v>
       </c>
       <c r="I28" t="n">
-        <v>648</v>
+        <v>612</v>
       </c>
       <c r="J28" t="n">
-        <v>623</v>
+        <v>754</v>
       </c>
       <c r="K28" t="n">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="L28" t="n">
-        <v>645.7</v>
+        <v>663.6</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="C29" t="n">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="D29" t="n">
-        <v>656</v>
+        <v>602</v>
       </c>
       <c r="E29" t="n">
-        <v>680</v>
+        <v>632</v>
       </c>
       <c r="F29" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="G29" t="n">
-        <v>635</v>
+        <v>735</v>
       </c>
       <c r="H29" t="n">
-        <v>657</v>
+        <v>740</v>
       </c>
       <c r="I29" t="n">
-        <v>704</v>
+        <v>647</v>
       </c>
       <c r="J29" t="n">
-        <v>619</v>
+        <v>810</v>
       </c>
       <c r="K29" t="n">
-        <v>638</v>
+        <v>733</v>
       </c>
       <c r="L29" t="n">
-        <v>652.2</v>
+        <v>682.3</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>666</v>
+        <v>649</v>
       </c>
       <c r="C30" t="n">
-        <v>681</v>
+        <v>752</v>
       </c>
       <c r="D30" t="n">
-        <v>730</v>
+        <v>581</v>
       </c>
       <c r="E30" t="n">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="F30" t="n">
-        <v>712</v>
+        <v>629</v>
       </c>
       <c r="G30" t="n">
-        <v>668</v>
+        <v>613</v>
       </c>
       <c r="H30" t="n">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="I30" t="n">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="J30" t="n">
-        <v>672</v>
+        <v>802</v>
       </c>
       <c r="K30" t="n">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="L30" t="n">
-        <v>675.2</v>
+        <v>668.4</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>880</v>
+        <v>764</v>
       </c>
       <c r="C31" t="n">
-        <v>782</v>
+        <v>820</v>
       </c>
       <c r="D31" t="n">
-        <v>718</v>
+        <v>861</v>
       </c>
       <c r="E31" t="n">
-        <v>772</v>
+        <v>824</v>
       </c>
       <c r="F31" t="n">
+        <v>712</v>
+      </c>
+      <c r="G31" t="n">
+        <v>744</v>
+      </c>
+      <c r="H31" t="n">
+        <v>723</v>
+      </c>
+      <c r="I31" t="n">
+        <v>769</v>
+      </c>
+      <c r="J31" t="n">
+        <v>736</v>
+      </c>
+      <c r="K31" t="n">
         <v>773</v>
       </c>
-      <c r="G31" t="n">
-        <v>752</v>
-      </c>
-      <c r="H31" t="n">
-        <v>719</v>
-      </c>
-      <c r="I31" t="n">
-        <v>802</v>
-      </c>
-      <c r="J31" t="n">
-        <v>665</v>
-      </c>
-      <c r="K31" t="n">
-        <v>754</v>
-      </c>
       <c r="L31" t="n">
-        <v>761.7</v>
+        <v>772.6</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>778</v>
+        <v>682</v>
       </c>
       <c r="C32" t="n">
-        <v>720</v>
+        <v>739</v>
       </c>
       <c r="D32" t="n">
-        <v>708</v>
+        <v>682</v>
       </c>
       <c r="E32" t="n">
-        <v>738</v>
+        <v>709</v>
       </c>
       <c r="F32" t="n">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="G32" t="n">
-        <v>702</v>
+        <v>675</v>
       </c>
       <c r="H32" t="n">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="I32" t="n">
-        <v>636</v>
+        <v>668</v>
       </c>
       <c r="J32" t="n">
-        <v>702</v>
+        <v>663</v>
       </c>
       <c r="K32" t="n">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="L32" t="n">
-        <v>706.4</v>
+        <v>692.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C33" t="n">
-        <v>765</v>
+        <v>692</v>
       </c>
       <c r="D33" t="n">
-        <v>754</v>
+        <v>719</v>
       </c>
       <c r="E33" t="n">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="F33" t="n">
-        <v>845</v>
+        <v>727</v>
       </c>
       <c r="G33" t="n">
-        <v>744</v>
+        <v>787</v>
       </c>
       <c r="H33" t="n">
-        <v>678</v>
+        <v>844</v>
       </c>
       <c r="I33" t="n">
-        <v>728</v>
+        <v>700</v>
       </c>
       <c r="J33" t="n">
-        <v>804</v>
+        <v>782</v>
       </c>
       <c r="K33" t="n">
-        <v>741</v>
+        <v>716</v>
       </c>
       <c r="L33" t="n">
-        <v>758.1</v>
+        <v>746.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>645</v>
+        <v>612</v>
       </c>
       <c r="C34" t="n">
+        <v>638</v>
+      </c>
+      <c r="D34" t="n">
+        <v>820</v>
+      </c>
+      <c r="E34" t="n">
+        <v>627</v>
+      </c>
+      <c r="F34" t="n">
         <v>704</v>
       </c>
-      <c r="D34" t="n">
-        <v>676</v>
-      </c>
-      <c r="E34" t="n">
-        <v>680</v>
-      </c>
-      <c r="F34" t="n">
-        <v>685</v>
-      </c>
       <c r="G34" t="n">
-        <v>699</v>
+        <v>673</v>
       </c>
       <c r="H34" t="n">
-        <v>709</v>
+        <v>626</v>
       </c>
       <c r="I34" t="n">
-        <v>700</v>
+        <v>742</v>
       </c>
       <c r="J34" t="n">
-        <v>698</v>
+        <v>626</v>
       </c>
       <c r="K34" t="n">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="L34" t="n">
-        <v>687.8</v>
+        <v>676.5</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>689</v>
+        <v>706</v>
       </c>
       <c r="C35" t="n">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D35" t="n">
-        <v>582</v>
+        <v>652</v>
       </c>
       <c r="E35" t="n">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="F35" t="n">
-        <v>576</v>
+        <v>609</v>
       </c>
       <c r="G35" t="n">
-        <v>581</v>
+        <v>629</v>
       </c>
       <c r="H35" t="n">
-        <v>597</v>
+        <v>673</v>
       </c>
       <c r="I35" t="n">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="J35" t="n">
-        <v>649</v>
+        <v>596</v>
       </c>
       <c r="K35" t="n">
-        <v>604</v>
+        <v>560</v>
       </c>
       <c r="L35" t="n">
-        <v>606.2</v>
+        <v>620.5</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>680</v>
+        <v>783</v>
       </c>
       <c r="C36" t="n">
-        <v>668</v>
+        <v>725</v>
       </c>
       <c r="D36" t="n">
-        <v>654</v>
+        <v>824</v>
       </c>
       <c r="E36" t="n">
-        <v>676</v>
+        <v>853</v>
       </c>
       <c r="F36" t="n">
-        <v>710</v>
+        <v>746</v>
       </c>
       <c r="G36" t="n">
-        <v>751</v>
+        <v>697</v>
       </c>
       <c r="H36" t="n">
+        <v>652</v>
+      </c>
+      <c r="I36" t="n">
+        <v>746</v>
+      </c>
+      <c r="J36" t="n">
         <v>688</v>
       </c>
-      <c r="I36" t="n">
-        <v>769</v>
-      </c>
-      <c r="J36" t="n">
-        <v>684</v>
-      </c>
       <c r="K36" t="n">
-        <v>750</v>
+        <v>774</v>
       </c>
       <c r="L36" t="n">
-        <v>703</v>
+        <v>748.8</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>667</v>
+        <v>774</v>
       </c>
       <c r="C37" t="n">
-        <v>822</v>
+        <v>654</v>
       </c>
       <c r="D37" t="n">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="E37" t="n">
-        <v>722</v>
+        <v>599</v>
       </c>
       <c r="F37" t="n">
-        <v>715</v>
+        <v>819</v>
       </c>
       <c r="G37" t="n">
-        <v>650</v>
+        <v>784</v>
       </c>
       <c r="H37" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="I37" t="n">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="J37" t="n">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="K37" t="n">
-        <v>797</v>
+        <v>615</v>
       </c>
       <c r="L37" t="n">
-        <v>726.7</v>
+        <v>714.9</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>605</v>
+        <v>658</v>
       </c>
       <c r="C38" t="n">
-        <v>590</v>
+        <v>634</v>
       </c>
       <c r="D38" t="n">
-        <v>714</v>
+        <v>678</v>
       </c>
       <c r="E38" t="n">
-        <v>608</v>
+        <v>642</v>
       </c>
       <c r="F38" t="n">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="G38" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H38" t="n">
-        <v>696</v>
+        <v>669</v>
       </c>
       <c r="I38" t="n">
-        <v>689</v>
+        <v>598</v>
       </c>
       <c r="J38" t="n">
-        <v>677</v>
+        <v>637</v>
       </c>
       <c r="K38" t="n">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="L38" t="n">
-        <v>641.2</v>
+        <v>640.1</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>593</v>
+        <v>660</v>
       </c>
       <c r="C39" t="n">
-        <v>601</v>
+        <v>663</v>
       </c>
       <c r="D39" t="n">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="E39" t="n">
-        <v>637</v>
+        <v>613</v>
       </c>
       <c r="F39" t="n">
-        <v>663</v>
+        <v>587</v>
       </c>
       <c r="G39" t="n">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="H39" t="n">
-        <v>600</v>
+        <v>549</v>
       </c>
       <c r="I39" t="n">
-        <v>607</v>
+        <v>675</v>
       </c>
       <c r="J39" t="n">
-        <v>522</v>
+        <v>699</v>
       </c>
       <c r="K39" t="n">
-        <v>613</v>
+        <v>574</v>
       </c>
       <c r="L39" t="n">
-        <v>605.2</v>
+        <v>625.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>872</v>
+        <v>856</v>
       </c>
       <c r="C40" t="n">
-        <v>623</v>
+        <v>720</v>
       </c>
       <c r="D40" t="n">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="E40" t="n">
-        <v>714</v>
+        <v>742</v>
       </c>
       <c r="F40" t="n">
-        <v>700</v>
+        <v>656</v>
       </c>
       <c r="G40" t="n">
-        <v>759</v>
+        <v>847</v>
       </c>
       <c r="H40" t="n">
-        <v>646</v>
+        <v>798</v>
       </c>
       <c r="I40" t="n">
-        <v>792</v>
+        <v>884</v>
       </c>
       <c r="J40" t="n">
-        <v>677</v>
+        <v>753</v>
       </c>
       <c r="K40" t="n">
-        <v>786</v>
+        <v>728</v>
       </c>
       <c r="L40" t="n">
-        <v>724.3</v>
+        <v>764.7</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C41" t="n">
-        <v>639</v>
+        <v>546</v>
       </c>
       <c r="D41" t="n">
-        <v>649</v>
+        <v>618</v>
       </c>
       <c r="E41" t="n">
-        <v>694</v>
+        <v>630</v>
       </c>
       <c r="F41" t="n">
-        <v>675</v>
+        <v>713</v>
       </c>
       <c r="G41" t="n">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="H41" t="n">
-        <v>635</v>
+        <v>699</v>
       </c>
       <c r="I41" t="n">
-        <v>545</v>
+        <v>699</v>
       </c>
       <c r="J41" t="n">
-        <v>706</v>
+        <v>607</v>
       </c>
       <c r="K41" t="n">
-        <v>585</v>
+        <v>725</v>
       </c>
       <c r="L41" t="n">
-        <v>643.1</v>
+        <v>653.8</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>706</v>
+        <v>637</v>
       </c>
       <c r="C42" t="n">
-        <v>726</v>
+        <v>791</v>
       </c>
       <c r="D42" t="n">
-        <v>586</v>
+        <v>746</v>
       </c>
       <c r="E42" t="n">
-        <v>726</v>
+        <v>650</v>
       </c>
       <c r="F42" t="n">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="G42" t="n">
-        <v>700</v>
+        <v>745</v>
       </c>
       <c r="H42" t="n">
-        <v>747</v>
+        <v>617</v>
       </c>
       <c r="I42" t="n">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="J42" t="n">
-        <v>624</v>
+        <v>744</v>
       </c>
       <c r="K42" t="n">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="L42" t="n">
-        <v>691.3</v>
+        <v>699.9</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>696</v>
+        <v>798</v>
       </c>
       <c r="C43" t="n">
-        <v>773</v>
+        <v>860</v>
       </c>
       <c r="D43" t="n">
-        <v>777</v>
+        <v>655</v>
       </c>
       <c r="E43" t="n">
-        <v>717</v>
+        <v>822</v>
       </c>
       <c r="F43" t="n">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="G43" t="n">
-        <v>886</v>
+        <v>684</v>
       </c>
       <c r="H43" t="n">
-        <v>700</v>
+        <v>785</v>
       </c>
       <c r="I43" t="n">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="J43" t="n">
-        <v>715</v>
+        <v>809</v>
       </c>
       <c r="K43" t="n">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="L43" t="n">
-        <v>733.5</v>
+        <v>752.4</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>599</v>
+        <v>657</v>
       </c>
       <c r="C44" t="n">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="D44" t="n">
-        <v>689</v>
+        <v>629</v>
       </c>
       <c r="E44" t="n">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="F44" t="n">
-        <v>622</v>
+        <v>724</v>
       </c>
       <c r="G44" t="n">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="H44" t="n">
-        <v>620</v>
+        <v>774</v>
       </c>
       <c r="I44" t="n">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="J44" t="n">
-        <v>645</v>
+        <v>699</v>
       </c>
       <c r="K44" t="n">
-        <v>641</v>
+        <v>623</v>
       </c>
       <c r="L44" t="n">
-        <v>637</v>
+        <v>671.1</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C45" t="n">
-        <v>775</v>
+        <v>627</v>
       </c>
       <c r="D45" t="n">
-        <v>687</v>
+        <v>721</v>
       </c>
       <c r="E45" t="n">
-        <v>770</v>
+        <v>706</v>
       </c>
       <c r="F45" t="n">
-        <v>614</v>
+        <v>759</v>
       </c>
       <c r="G45" t="n">
-        <v>830</v>
+        <v>768</v>
       </c>
       <c r="H45" t="n">
-        <v>687</v>
+        <v>662</v>
       </c>
       <c r="I45" t="n">
-        <v>742</v>
+        <v>688</v>
       </c>
       <c r="J45" t="n">
-        <v>771</v>
+        <v>827</v>
       </c>
       <c r="K45" t="n">
-        <v>737</v>
+        <v>672</v>
       </c>
       <c r="L45" t="n">
-        <v>731.4</v>
+        <v>712.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C46" t="n">
+        <v>673</v>
+      </c>
+      <c r="D46" t="n">
+        <v>700</v>
+      </c>
+      <c r="E46" t="n">
         <v>717</v>
       </c>
-      <c r="D46" t="n">
-        <v>663</v>
-      </c>
-      <c r="E46" t="n">
-        <v>724</v>
-      </c>
       <c r="F46" t="n">
-        <v>635</v>
+        <v>726</v>
       </c>
       <c r="G46" t="n">
-        <v>642</v>
+        <v>695</v>
       </c>
       <c r="H46" t="n">
-        <v>730</v>
+        <v>655</v>
       </c>
       <c r="I46" t="n">
-        <v>681</v>
+        <v>647</v>
       </c>
       <c r="J46" t="n">
-        <v>717</v>
+        <v>770</v>
       </c>
       <c r="K46" t="n">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="L46" t="n">
-        <v>689.3</v>
+        <v>699.3</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>695</v>
+        <v>633</v>
       </c>
       <c r="C47" t="n">
-        <v>574</v>
+        <v>607</v>
       </c>
       <c r="D47" t="n">
-        <v>562</v>
+        <v>782</v>
       </c>
       <c r="E47" t="n">
-        <v>634</v>
+        <v>673</v>
       </c>
       <c r="F47" t="n">
-        <v>604</v>
+        <v>654</v>
       </c>
       <c r="G47" t="n">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="H47" t="n">
-        <v>603</v>
+        <v>670</v>
       </c>
       <c r="I47" t="n">
-        <v>707</v>
+        <v>572</v>
       </c>
       <c r="J47" t="n">
-        <v>682</v>
+        <v>783</v>
       </c>
       <c r="K47" t="n">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="L47" t="n">
-        <v>631</v>
+        <v>666</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>716</v>
+        <v>757</v>
       </c>
       <c r="C48" t="n">
-        <v>810</v>
+        <v>724</v>
       </c>
       <c r="D48" t="n">
-        <v>719</v>
+        <v>733</v>
       </c>
       <c r="E48" t="n">
-        <v>794</v>
+        <v>751</v>
       </c>
       <c r="F48" t="n">
-        <v>734</v>
+        <v>780</v>
       </c>
       <c r="G48" t="n">
-        <v>851</v>
+        <v>757</v>
       </c>
       <c r="H48" t="n">
-        <v>741</v>
+        <v>815</v>
       </c>
       <c r="I48" t="n">
-        <v>738</v>
+        <v>718</v>
       </c>
       <c r="J48" t="n">
-        <v>765</v>
+        <v>718</v>
       </c>
       <c r="K48" t="n">
-        <v>912</v>
+        <v>702</v>
       </c>
       <c r="L48" t="n">
-        <v>778</v>
+        <v>745.5</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>689</v>
+        <v>828</v>
       </c>
       <c r="C49" t="n">
-        <v>629</v>
+        <v>760</v>
       </c>
       <c r="D49" t="n">
-        <v>788</v>
+        <v>747</v>
       </c>
       <c r="E49" t="n">
-        <v>767</v>
+        <v>702</v>
       </c>
       <c r="F49" t="n">
-        <v>767</v>
+        <v>813</v>
       </c>
       <c r="G49" t="n">
-        <v>751</v>
+        <v>845</v>
       </c>
       <c r="H49" t="n">
-        <v>859</v>
+        <v>792</v>
       </c>
       <c r="I49" t="n">
-        <v>826</v>
+        <v>705</v>
       </c>
       <c r="J49" t="n">
-        <v>757</v>
+        <v>819</v>
       </c>
       <c r="K49" t="n">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="L49" t="n">
-        <v>765</v>
+        <v>784</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="C50" t="n">
-        <v>702</v>
+        <v>771</v>
       </c>
       <c r="D50" t="n">
-        <v>784</v>
+        <v>726</v>
       </c>
       <c r="E50" t="n">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="F50" t="n">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="G50" t="n">
-        <v>677</v>
+        <v>758</v>
       </c>
       <c r="H50" t="n">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I50" t="n">
-        <v>670</v>
+        <v>781</v>
       </c>
       <c r="J50" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="K50" t="n">
-        <v>791</v>
+        <v>679</v>
       </c>
       <c r="L50" t="n">
-        <v>711.2</v>
+        <v>721.1</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>682</v>
+        <v>742</v>
       </c>
       <c r="C51" t="n">
-        <v>726</v>
+        <v>692</v>
       </c>
       <c r="D51" t="n">
-        <v>651</v>
+        <v>693</v>
       </c>
       <c r="E51" t="n">
-        <v>691</v>
+        <v>804</v>
       </c>
       <c r="F51" t="n">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="G51" t="n">
-        <v>667</v>
+        <v>737</v>
       </c>
       <c r="H51" t="n">
-        <v>599</v>
+        <v>789</v>
       </c>
       <c r="I51" t="n">
-        <v>749</v>
+        <v>700</v>
       </c>
       <c r="J51" t="n">
-        <v>726</v>
+        <v>799</v>
       </c>
       <c r="K51" t="n">
-        <v>610</v>
+        <v>644</v>
       </c>
       <c r="L51" t="n">
-        <v>682.6</v>
+        <v>731.1</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>690.54</v>
+        <v>699.5</v>
       </c>
       <c r="C52" t="n">
-        <v>682.88</v>
+        <v>696.5</v>
       </c>
       <c r="D52" t="n">
-        <v>683.9</v>
+        <v>687.74</v>
       </c>
       <c r="E52" t="n">
-        <v>698.9400000000001</v>
+        <v>687.16</v>
       </c>
       <c r="F52" t="n">
-        <v>679.14</v>
+        <v>688.5599999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>688.42</v>
+        <v>689.72</v>
       </c>
       <c r="H52" t="n">
-        <v>679.22</v>
+        <v>698</v>
       </c>
       <c r="I52" t="n">
-        <v>693.1799999999999</v>
+        <v>685.76</v>
       </c>
       <c r="J52" t="n">
-        <v>693.62</v>
+        <v>700.64</v>
       </c>
       <c r="K52" t="n">
-        <v>691.7</v>
+        <v>681.1799999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>688.1539999999998</v>
+        <v>691.4759999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.579345226287842</v>
+        <v>4.166105031967163</v>
       </c>
       <c r="C2" t="n">
-        <v>5.130204916000366</v>
+        <v>4.477129936218262</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0932776927948</v>
+        <v>4.638845920562744</v>
       </c>
       <c r="E2" t="n">
-        <v>4.80551552772522</v>
+        <v>4.447272539138794</v>
       </c>
       <c r="F2" t="n">
-        <v>4.239969730377197</v>
+        <v>4.456252336502075</v>
       </c>
       <c r="G2" t="n">
-        <v>6.365566968917847</v>
+        <v>4.39470911026001</v>
       </c>
       <c r="H2" t="n">
-        <v>4.581125259399414</v>
+        <v>4.794862985610962</v>
       </c>
       <c r="I2" t="n">
-        <v>4.857364654541016</v>
+        <v>4.064238548278809</v>
       </c>
       <c r="J2" t="n">
-        <v>5.587501764297485</v>
+        <v>4.183187007904053</v>
       </c>
       <c r="K2" t="n">
-        <v>4.86637806892395</v>
+        <v>4.936552047729492</v>
       </c>
       <c r="L2" t="n">
-        <v>5.010624980926513</v>
+        <v>4.455915546417236</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.63621973991394</v>
+        <v>4.764882802963257</v>
       </c>
       <c r="C3" t="n">
-        <v>4.94692850112915</v>
+        <v>5.931455373764038</v>
       </c>
       <c r="D3" t="n">
-        <v>4.875117540359497</v>
+        <v>5.326861143112183</v>
       </c>
       <c r="E3" t="n">
-        <v>5.02626895904541</v>
+        <v>4.682845592498779</v>
       </c>
       <c r="F3" t="n">
-        <v>5.016261100769043</v>
+        <v>4.835816144943237</v>
       </c>
       <c r="G3" t="n">
-        <v>4.708520174026489</v>
+        <v>4.634717702865601</v>
       </c>
       <c r="H3" t="n">
-        <v>5.984907150268555</v>
+        <v>5.911106824874878</v>
       </c>
       <c r="I3" t="n">
-        <v>5.303061246871948</v>
+        <v>4.730897426605225</v>
       </c>
       <c r="J3" t="n">
-        <v>5.684532403945923</v>
+        <v>5.050292015075684</v>
       </c>
       <c r="K3" t="n">
-        <v>5.154908657073975</v>
+        <v>4.997239351272583</v>
       </c>
       <c r="L3" t="n">
-        <v>5.133672547340393</v>
+        <v>5.086611437797546</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.357464075088501</v>
+        <v>4.225518226623535</v>
       </c>
       <c r="C4" t="n">
-        <v>4.277644634246826</v>
+        <v>4.053731918334961</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6048424243927</v>
+        <v>3.936415195465088</v>
       </c>
       <c r="E4" t="n">
-        <v>3.837259292602539</v>
+        <v>3.897826194763184</v>
       </c>
       <c r="F4" t="n">
-        <v>3.815284729003906</v>
+        <v>3.777528285980225</v>
       </c>
       <c r="G4" t="n">
-        <v>4.085124731063843</v>
+        <v>3.968069076538086</v>
       </c>
       <c r="H4" t="n">
-        <v>4.68961501121521</v>
+        <v>3.957314014434814</v>
       </c>
       <c r="I4" t="n">
-        <v>3.900174856185913</v>
+        <v>3.888810873031616</v>
       </c>
       <c r="J4" t="n">
-        <v>4.521015405654907</v>
+        <v>4.097073078155518</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7210373878479</v>
+        <v>3.906409978866577</v>
       </c>
       <c r="L4" t="n">
-        <v>4.080946254730224</v>
+        <v>3.97086968421936</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.128010988235474</v>
+        <v>4.437430143356323</v>
       </c>
       <c r="C5" t="n">
-        <v>4.765956163406372</v>
+        <v>4.106534004211426</v>
       </c>
       <c r="D5" t="n">
-        <v>4.386001348495483</v>
+        <v>4.518190860748291</v>
       </c>
       <c r="E5" t="n">
-        <v>4.098861455917358</v>
+        <v>4.76366114616394</v>
       </c>
       <c r="F5" t="n">
-        <v>3.996659517288208</v>
+        <v>4.021673679351807</v>
       </c>
       <c r="G5" t="n">
-        <v>4.360180854797363</v>
+        <v>5.091823101043701</v>
       </c>
       <c r="H5" t="n">
-        <v>4.272404432296753</v>
+        <v>4.147690057754517</v>
       </c>
       <c r="I5" t="n">
-        <v>3.902348518371582</v>
+        <v>4.237260580062866</v>
       </c>
       <c r="J5" t="n">
-        <v>3.958963632583618</v>
+        <v>4.156222105026245</v>
       </c>
       <c r="K5" t="n">
-        <v>4.46645975112915</v>
+        <v>4.114533185958862</v>
       </c>
       <c r="L5" t="n">
-        <v>4.233584666252137</v>
+        <v>4.359501886367798</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>4.437762260437012</v>
+        <v>4.481680631637573</v>
       </c>
       <c r="C6" t="n">
-        <v>3.805315017700195</v>
+        <v>4.184137582778931</v>
       </c>
       <c r="D6" t="n">
-        <v>4.237244844436646</v>
+        <v>5.523858070373535</v>
       </c>
       <c r="E6" t="n">
-        <v>4.651691198348999</v>
+        <v>4.251400470733643</v>
       </c>
       <c r="F6" t="n">
-        <v>3.973395586013794</v>
+        <v>4.112363815307617</v>
       </c>
       <c r="G6" t="n">
-        <v>4.168416738510132</v>
+        <v>4.277914524078369</v>
       </c>
       <c r="H6" t="n">
-        <v>4.129001140594482</v>
+        <v>4.61022686958313</v>
       </c>
       <c r="I6" t="n">
-        <v>3.685953140258789</v>
+        <v>4.249892950057983</v>
       </c>
       <c r="J6" t="n">
-        <v>4.675456523895264</v>
+        <v>4.242588043212891</v>
       </c>
       <c r="K6" t="n">
-        <v>4.120301008224487</v>
+        <v>4.590094089508057</v>
       </c>
       <c r="L6" t="n">
-        <v>4.18845374584198</v>
+        <v>4.452415704727173</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>4.558165550231934</v>
+        <v>4.465216636657715</v>
       </c>
       <c r="C7" t="n">
-        <v>3.917348146438599</v>
+        <v>4.041699647903442</v>
       </c>
       <c r="D7" t="n">
-        <v>3.988677501678467</v>
+        <v>4.011314868927002</v>
       </c>
       <c r="E7" t="n">
-        <v>4.856388092041016</v>
+        <v>4.753941774368286</v>
       </c>
       <c r="F7" t="n">
-        <v>3.777188301086426</v>
+        <v>4.317687273025513</v>
       </c>
       <c r="G7" t="n">
-        <v>4.200388431549072</v>
+        <v>4.81028938293457</v>
       </c>
       <c r="H7" t="n">
-        <v>4.031741142272949</v>
+        <v>4.207337856292725</v>
       </c>
       <c r="I7" t="n">
-        <v>5.89462947845459</v>
+        <v>4.178480386734009</v>
       </c>
       <c r="J7" t="n">
-        <v>4.113038539886475</v>
+        <v>4.013850927352905</v>
       </c>
       <c r="K7" t="n">
-        <v>5.277134656906128</v>
+        <v>4.238885641098022</v>
       </c>
       <c r="L7" t="n">
-        <v>4.461469984054565</v>
+        <v>4.303870439529419</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.823736190795898</v>
+        <v>5.018072605133057</v>
       </c>
       <c r="C8" t="n">
-        <v>4.669161081314087</v>
+        <v>4.496826648712158</v>
       </c>
       <c r="D8" t="n">
-        <v>4.360406637191772</v>
+        <v>4.332158327102661</v>
       </c>
       <c r="E8" t="n">
-        <v>4.553949117660522</v>
+        <v>4.795213460922241</v>
       </c>
       <c r="F8" t="n">
-        <v>5.202576160430908</v>
+        <v>5.398306131362915</v>
       </c>
       <c r="G8" t="n">
-        <v>5.066299676895142</v>
+        <v>4.394673824310303</v>
       </c>
       <c r="H8" t="n">
-        <v>4.830351829528809</v>
+        <v>5.172374725341797</v>
       </c>
       <c r="I8" t="n">
-        <v>4.834822177886963</v>
+        <v>4.604104280471802</v>
       </c>
       <c r="J8" t="n">
-        <v>5.698105096817017</v>
+        <v>4.639811038970947</v>
       </c>
       <c r="K8" t="n">
-        <v>4.363947153091431</v>
+        <v>4.862104654312134</v>
       </c>
       <c r="L8" t="n">
-        <v>4.840335512161255</v>
+        <v>4.771364569664001</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.970437288284302</v>
+        <v>3.885325193405151</v>
       </c>
       <c r="C9" t="n">
-        <v>3.90461254119873</v>
+        <v>4.065277576446533</v>
       </c>
       <c r="D9" t="n">
-        <v>4.417216539382935</v>
+        <v>3.834443092346191</v>
       </c>
       <c r="E9" t="n">
-        <v>4.606706619262695</v>
+        <v>4.023870229721069</v>
       </c>
       <c r="F9" t="n">
-        <v>3.931042432785034</v>
+        <v>4.10687518119812</v>
       </c>
       <c r="G9" t="n">
-        <v>4.15797758102417</v>
+        <v>3.911489963531494</v>
       </c>
       <c r="H9" t="n">
-        <v>4.788918495178223</v>
+        <v>4.140890836715698</v>
       </c>
       <c r="I9" t="n">
-        <v>3.837253332138062</v>
+        <v>3.987574338912964</v>
       </c>
       <c r="J9" t="n">
-        <v>3.742988348007202</v>
+        <v>4.054350614547729</v>
       </c>
       <c r="K9" t="n">
-        <v>3.89360785484314</v>
+        <v>4.185307741165161</v>
       </c>
       <c r="L9" t="n">
-        <v>4.125076103210449</v>
+        <v>4.019540476799011</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.851154804229736</v>
+        <v>5.739005327224731</v>
       </c>
       <c r="C10" t="n">
-        <v>5.037195444107056</v>
+        <v>5.41407585144043</v>
       </c>
       <c r="D10" t="n">
-        <v>5.403249025344849</v>
+        <v>6.494092226028442</v>
       </c>
       <c r="E10" t="n">
-        <v>5.249577760696411</v>
+        <v>5.193048715591431</v>
       </c>
       <c r="F10" t="n">
-        <v>5.540199518203735</v>
+        <v>5.163626909255981</v>
       </c>
       <c r="G10" t="n">
-        <v>5.405271291732788</v>
+        <v>5.965759754180908</v>
       </c>
       <c r="H10" t="n">
-        <v>5.365875720977783</v>
+        <v>5.583483457565308</v>
       </c>
       <c r="I10" t="n">
-        <v>5.95009183883667</v>
+        <v>5.58522367477417</v>
       </c>
       <c r="J10" t="n">
-        <v>5.449671506881714</v>
+        <v>5.191778182983398</v>
       </c>
       <c r="K10" t="n">
-        <v>4.978486776351929</v>
+        <v>6.058747053146362</v>
       </c>
       <c r="L10" t="n">
-        <v>5.323077368736267</v>
+        <v>5.638884115219116</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.518868207931519</v>
+        <v>4.890211343765259</v>
       </c>
       <c r="C11" t="n">
-        <v>4.801534175872803</v>
+        <v>5.280463933944702</v>
       </c>
       <c r="D11" t="n">
-        <v>5.127223253250122</v>
+        <v>4.676712274551392</v>
       </c>
       <c r="E11" t="n">
-        <v>5.078951835632324</v>
+        <v>5.210310220718384</v>
       </c>
       <c r="F11" t="n">
-        <v>4.417292594909668</v>
+        <v>5.59912109375</v>
       </c>
       <c r="G11" t="n">
-        <v>4.616249322891235</v>
+        <v>4.630968570709229</v>
       </c>
       <c r="H11" t="n">
-        <v>4.537957429885864</v>
+        <v>5.691882610321045</v>
       </c>
       <c r="I11" t="n">
-        <v>5.769839286804199</v>
+        <v>4.743255376815796</v>
       </c>
       <c r="J11" t="n">
-        <v>4.454220056533813</v>
+        <v>4.62028694152832</v>
       </c>
       <c r="K11" t="n">
-        <v>4.885082006454468</v>
+        <v>5.152972221374512</v>
       </c>
       <c r="L11" t="n">
-        <v>4.820721817016602</v>
+        <v>5.049618458747863</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.893076419830322</v>
+        <v>4.472437381744385</v>
       </c>
       <c r="C12" t="n">
-        <v>4.43791937828064</v>
+        <v>4.638740301132202</v>
       </c>
       <c r="D12" t="n">
-        <v>4.111843109130859</v>
+        <v>4.26318359375</v>
       </c>
       <c r="E12" t="n">
-        <v>4.046498537063599</v>
+        <v>4.373442411422729</v>
       </c>
       <c r="F12" t="n">
-        <v>3.929320335388184</v>
+        <v>4.101322412490845</v>
       </c>
       <c r="G12" t="n">
-        <v>4.520853996276855</v>
+        <v>4.421472072601318</v>
       </c>
       <c r="H12" t="n">
-        <v>4.684320211410522</v>
+        <v>4.501532554626465</v>
       </c>
       <c r="I12" t="n">
-        <v>4.349225282669067</v>
+        <v>5.022429943084717</v>
       </c>
       <c r="J12" t="n">
-        <v>4.301060438156128</v>
+        <v>4.57545804977417</v>
       </c>
       <c r="K12" t="n">
-        <v>4.395830869674683</v>
+        <v>4.330641031265259</v>
       </c>
       <c r="L12" t="n">
-        <v>4.266994857788086</v>
+        <v>4.470065975189209</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.96830415725708</v>
+        <v>5.159871816635132</v>
       </c>
       <c r="C13" t="n">
-        <v>6.106998920440674</v>
+        <v>4.822903394699097</v>
       </c>
       <c r="D13" t="n">
-        <v>7.016673564910889</v>
+        <v>5.351072072982788</v>
       </c>
       <c r="E13" t="n">
-        <v>5.72740650177002</v>
+        <v>5.15291953086853</v>
       </c>
       <c r="F13" t="n">
-        <v>5.075915336608887</v>
+        <v>5.162701845169067</v>
       </c>
       <c r="G13" t="n">
-        <v>5.890730142593384</v>
+        <v>5.572580337524414</v>
       </c>
       <c r="H13" t="n">
-        <v>5.132486581802368</v>
+        <v>4.848061323165894</v>
       </c>
       <c r="I13" t="n">
-        <v>6.709295988082886</v>
+        <v>5.672614336013794</v>
       </c>
       <c r="J13" t="n">
-        <v>5.387357473373413</v>
+        <v>5.781855583190918</v>
       </c>
       <c r="K13" t="n">
-        <v>4.706562042236328</v>
+        <v>4.642735481262207</v>
       </c>
       <c r="L13" t="n">
-        <v>5.972173070907592</v>
+        <v>5.216731572151184</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.216264009475708</v>
+        <v>4.494117736816406</v>
       </c>
       <c r="C14" t="n">
-        <v>4.408804178237915</v>
+        <v>4.974334716796875</v>
       </c>
       <c r="D14" t="n">
-        <v>4.46416187286377</v>
+        <v>4.533679008483887</v>
       </c>
       <c r="E14" t="n">
-        <v>5.040181636810303</v>
+        <v>4.442979335784912</v>
       </c>
       <c r="F14" t="n">
-        <v>4.156492948532104</v>
+        <v>4.515646457672119</v>
       </c>
       <c r="G14" t="n">
-        <v>4.42496395111084</v>
+        <v>4.597957611083984</v>
       </c>
       <c r="H14" t="n">
-        <v>4.875672578811646</v>
+        <v>5.700881958007812</v>
       </c>
       <c r="I14" t="n">
-        <v>4.45267915725708</v>
+        <v>4.570471048355103</v>
       </c>
       <c r="J14" t="n">
-        <v>4.848665952682495</v>
+        <v>4.595580101013184</v>
       </c>
       <c r="K14" t="n">
-        <v>4.708545684814453</v>
+        <v>4.961857557296753</v>
       </c>
       <c r="L14" t="n">
-        <v>4.559643197059631</v>
+        <v>4.738750553131103</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.953405141830444</v>
+        <v>5.215205907821655</v>
       </c>
       <c r="C15" t="n">
-        <v>4.653194904327393</v>
+        <v>5.491636514663696</v>
       </c>
       <c r="D15" t="n">
-        <v>5.032191038131714</v>
+        <v>5.023109912872314</v>
       </c>
       <c r="E15" t="n">
-        <v>4.605294942855835</v>
+        <v>5.472748756408691</v>
       </c>
       <c r="F15" t="n">
-        <v>5.468664884567261</v>
+        <v>5.052551984786987</v>
       </c>
       <c r="G15" t="n">
-        <v>4.350110769271851</v>
+        <v>5.060431957244873</v>
       </c>
       <c r="H15" t="n">
-        <v>4.527249813079834</v>
+        <v>5.14016056060791</v>
       </c>
       <c r="I15" t="n">
-        <v>4.849383115768433</v>
+        <v>4.997592926025391</v>
       </c>
       <c r="J15" t="n">
-        <v>5.029093503952026</v>
+        <v>5.497692823410034</v>
       </c>
       <c r="K15" t="n">
-        <v>4.579144716262817</v>
+        <v>4.48400354385376</v>
       </c>
       <c r="L15" t="n">
-        <v>4.804773283004761</v>
+        <v>5.143513488769531</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.184175491333008</v>
+        <v>5.112125396728516</v>
       </c>
       <c r="C16" t="n">
-        <v>4.171511888504028</v>
+        <v>4.531022787094116</v>
       </c>
       <c r="D16" t="n">
-        <v>4.657407522201538</v>
+        <v>4.938637971878052</v>
       </c>
       <c r="E16" t="n">
-        <v>4.408180713653564</v>
+        <v>4.470685482025146</v>
       </c>
       <c r="F16" t="n">
-        <v>5.192502975463867</v>
+        <v>4.373902320861816</v>
       </c>
       <c r="G16" t="n">
-        <v>3.983242988586426</v>
+        <v>4.397626876831055</v>
       </c>
       <c r="H16" t="n">
-        <v>4.452217102050781</v>
+        <v>4.341387748718262</v>
       </c>
       <c r="I16" t="n">
-        <v>4.0836181640625</v>
+        <v>4.413583993911743</v>
       </c>
       <c r="J16" t="n">
-        <v>4.086108446121216</v>
+        <v>4.723205327987671</v>
       </c>
       <c r="K16" t="n">
-        <v>4.953204154968262</v>
+        <v>4.600204944610596</v>
       </c>
       <c r="L16" t="n">
-        <v>4.417216944694519</v>
+        <v>4.590238285064697</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.051690816879272</v>
+        <v>4.656335353851318</v>
       </c>
       <c r="C17" t="n">
-        <v>4.297609567642212</v>
+        <v>4.900205850601196</v>
       </c>
       <c r="D17" t="n">
-        <v>4.519010305404663</v>
+        <v>4.485772132873535</v>
       </c>
       <c r="E17" t="n">
-        <v>4.199321985244751</v>
+        <v>4.803678035736084</v>
       </c>
       <c r="F17" t="n">
-        <v>4.473455190658569</v>
+        <v>4.649193525314331</v>
       </c>
       <c r="G17" t="n">
-        <v>4.264906406402588</v>
+        <v>5.644554138183594</v>
       </c>
       <c r="H17" t="n">
-        <v>4.488848209381104</v>
+        <v>4.320907592773438</v>
       </c>
       <c r="I17" t="n">
-        <v>4.232011318206787</v>
+        <v>4.772210836410522</v>
       </c>
       <c r="J17" t="n">
-        <v>4.801576375961304</v>
+        <v>4.678903579711914</v>
       </c>
       <c r="K17" t="n">
-        <v>4.886304140090942</v>
+        <v>4.59018874168396</v>
       </c>
       <c r="L17" t="n">
-        <v>4.421473431587219</v>
+        <v>4.750194978713989</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>5.638413667678833</v>
+        <v>4.889049053192139</v>
       </c>
       <c r="C18" t="n">
-        <v>4.717291355133057</v>
+        <v>5.290430068969727</v>
       </c>
       <c r="D18" t="n">
-        <v>4.647209405899048</v>
+        <v>4.459216833114624</v>
       </c>
       <c r="E18" t="n">
-        <v>4.781578540802002</v>
+        <v>4.848397493362427</v>
       </c>
       <c r="F18" t="n">
-        <v>4.806540966033936</v>
+        <v>5.085224628448486</v>
       </c>
       <c r="G18" t="n">
-        <v>5.371172666549683</v>
+        <v>5.034060716629028</v>
       </c>
       <c r="H18" t="n">
-        <v>4.922728300094604</v>
+        <v>4.574358940124512</v>
       </c>
       <c r="I18" t="n">
-        <v>5.411941289901733</v>
+        <v>5.336984634399414</v>
       </c>
       <c r="J18" t="n">
-        <v>4.407565355300903</v>
+        <v>4.742551803588867</v>
       </c>
       <c r="K18" t="n">
-        <v>4.299348115921021</v>
+        <v>4.923186063766479</v>
       </c>
       <c r="L18" t="n">
-        <v>4.900378966331482</v>
+        <v>4.91834602355957</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.03849196434021</v>
+        <v>4.651527404785156</v>
       </c>
       <c r="C19" t="n">
-        <v>4.404564619064331</v>
+        <v>4.539525747299194</v>
       </c>
       <c r="D19" t="n">
-        <v>4.02454662322998</v>
+        <v>4.241185426712036</v>
       </c>
       <c r="E19" t="n">
-        <v>4.861926317214966</v>
+        <v>4.643949270248413</v>
       </c>
       <c r="F19" t="n">
-        <v>4.692862987518311</v>
+        <v>4.363868951797485</v>
       </c>
       <c r="G19" t="n">
-        <v>4.429992914199829</v>
+        <v>4.274069786071777</v>
       </c>
       <c r="H19" t="n">
-        <v>4.331059217453003</v>
+        <v>4.60977029800415</v>
       </c>
       <c r="I19" t="n">
-        <v>4.300362825393677</v>
+        <v>4.60658860206604</v>
       </c>
       <c r="J19" t="n">
-        <v>4.33798885345459</v>
+        <v>4.660216808319092</v>
       </c>
       <c r="K19" t="n">
-        <v>4.634308099746704</v>
+        <v>4.200419187545776</v>
       </c>
       <c r="L19" t="n">
-        <v>4.40561044216156</v>
+        <v>4.479112148284912</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.395293951034546</v>
+        <v>5.468098878860474</v>
       </c>
       <c r="C20" t="n">
-        <v>4.929005861282349</v>
+        <v>5.065400123596191</v>
       </c>
       <c r="D20" t="n">
-        <v>5.100532054901123</v>
+        <v>5.151074171066284</v>
       </c>
       <c r="E20" t="n">
-        <v>5.200793743133545</v>
+        <v>5.506068468093872</v>
       </c>
       <c r="F20" t="n">
-        <v>5.277095556259155</v>
+        <v>5.239344358444214</v>
       </c>
       <c r="G20" t="n">
-        <v>5.438190937042236</v>
+        <v>6.200591087341309</v>
       </c>
       <c r="H20" t="n">
-        <v>5.544385194778442</v>
+        <v>6.098667860031128</v>
       </c>
       <c r="I20" t="n">
-        <v>4.829711675643921</v>
+        <v>5.073062896728516</v>
       </c>
       <c r="J20" t="n">
-        <v>4.550427436828613</v>
+        <v>4.988178730010986</v>
       </c>
       <c r="K20" t="n">
-        <v>4.772355318069458</v>
+        <v>5.434833526611328</v>
       </c>
       <c r="L20" t="n">
-        <v>5.103779172897339</v>
+        <v>5.42253201007843</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.893057346343994</v>
+        <v>5.595820665359497</v>
       </c>
       <c r="C21" t="n">
-        <v>4.55940580368042</v>
+        <v>6.283883571624756</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405801057815552</v>
+        <v>4.738779544830322</v>
       </c>
       <c r="E21" t="n">
-        <v>5.499997615814209</v>
+        <v>4.403420925140381</v>
       </c>
       <c r="F21" t="n">
-        <v>3.999484300613403</v>
+        <v>4.975522994995117</v>
       </c>
       <c r="G21" t="n">
-        <v>5.108054637908936</v>
+        <v>4.999530076980591</v>
       </c>
       <c r="H21" t="n">
-        <v>5.319692850112915</v>
+        <v>5.805503606796265</v>
       </c>
       <c r="I21" t="n">
-        <v>4.328757762908936</v>
+        <v>4.91647744178772</v>
       </c>
       <c r="J21" t="n">
-        <v>5.24739933013916</v>
+        <v>6.55191445350647</v>
       </c>
       <c r="K21" t="n">
-        <v>4.611008167266846</v>
+        <v>4.392828941345215</v>
       </c>
       <c r="L21" t="n">
-        <v>4.797265887260437</v>
+        <v>5.266368222236633</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.531733274459839</v>
+        <v>5.372653245925903</v>
       </c>
       <c r="C22" t="n">
-        <v>5.260829210281372</v>
+        <v>4.659059762954712</v>
       </c>
       <c r="D22" t="n">
-        <v>5.042700290679932</v>
+        <v>5.203674793243408</v>
       </c>
       <c r="E22" t="n">
-        <v>4.305569171905518</v>
+        <v>4.91011118888855</v>
       </c>
       <c r="F22" t="n">
-        <v>4.752413988113403</v>
+        <v>4.881728649139404</v>
       </c>
       <c r="G22" t="n">
-        <v>4.758558988571167</v>
+        <v>4.991715908050537</v>
       </c>
       <c r="H22" t="n">
-        <v>4.570880651473999</v>
+        <v>4.588253259658813</v>
       </c>
       <c r="I22" t="n">
-        <v>5.43468976020813</v>
+        <v>5.314383268356323</v>
       </c>
       <c r="J22" t="n">
-        <v>4.465648889541626</v>
+        <v>4.767238616943359</v>
       </c>
       <c r="K22" t="n">
-        <v>4.62822437286377</v>
+        <v>5.479583263397217</v>
       </c>
       <c r="L22" t="n">
-        <v>4.775124859809876</v>
+        <v>5.016840195655822</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.794624328613281</v>
+        <v>4.714954137802124</v>
       </c>
       <c r="C23" t="n">
-        <v>4.1993408203125</v>
+        <v>4.487642526626587</v>
       </c>
       <c r="D23" t="n">
-        <v>4.055207490921021</v>
+        <v>4.569019556045532</v>
       </c>
       <c r="E23" t="n">
-        <v>4.294063091278076</v>
+        <v>4.823490142822266</v>
       </c>
       <c r="F23" t="n">
-        <v>4.03225040435791</v>
+        <v>4.605409860610962</v>
       </c>
       <c r="G23" t="n">
-        <v>3.943464756011963</v>
+        <v>4.600512027740479</v>
       </c>
       <c r="H23" t="n">
-        <v>3.966900587081909</v>
+        <v>4.472312211990356</v>
       </c>
       <c r="I23" t="n">
-        <v>4.387338638305664</v>
+        <v>4.639079093933105</v>
       </c>
       <c r="J23" t="n">
-        <v>4.039669513702393</v>
+        <v>4.556844472885132</v>
       </c>
       <c r="K23" t="n">
-        <v>4.043480157852173</v>
+        <v>4.537222623825073</v>
       </c>
       <c r="L23" t="n">
-        <v>4.175633978843689</v>
+        <v>4.600648665428162</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.554184913635254</v>
+        <v>4.821240186691284</v>
       </c>
       <c r="C24" t="n">
-        <v>5.312697410583496</v>
+        <v>4.448860883712769</v>
       </c>
       <c r="D24" t="n">
-        <v>5.388494968414307</v>
+        <v>5.23744010925293</v>
       </c>
       <c r="E24" t="n">
-        <v>4.382608652114868</v>
+        <v>5.122068405151367</v>
       </c>
       <c r="F24" t="n">
-        <v>4.816520690917969</v>
+        <v>5.242561340332031</v>
       </c>
       <c r="G24" t="n">
-        <v>5.008986473083496</v>
+        <v>5.313841581344604</v>
       </c>
       <c r="H24" t="n">
-        <v>4.692339181900024</v>
+        <v>4.789899826049805</v>
       </c>
       <c r="I24" t="n">
-        <v>4.914770603179932</v>
+        <v>5.279687166213989</v>
       </c>
       <c r="J24" t="n">
-        <v>4.162691831588745</v>
+        <v>4.820882797241211</v>
       </c>
       <c r="K24" t="n">
-        <v>4.573125123977661</v>
+        <v>5.427443504333496</v>
       </c>
       <c r="L24" t="n">
-        <v>4.780641984939575</v>
+        <v>5.050392580032349</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.720414400100708</v>
+        <v>4.740548610687256</v>
       </c>
       <c r="C25" t="n">
-        <v>4.703533887863159</v>
+        <v>4.572908639907837</v>
       </c>
       <c r="D25" t="n">
-        <v>4.611258745193481</v>
+        <v>4.485745191574097</v>
       </c>
       <c r="E25" t="n">
-        <v>4.608270168304443</v>
+        <v>5.060487747192383</v>
       </c>
       <c r="F25" t="n">
-        <v>4.441271781921387</v>
+        <v>4.896317958831787</v>
       </c>
       <c r="G25" t="n">
-        <v>4.565892934799194</v>
+        <v>4.563207626342773</v>
       </c>
       <c r="H25" t="n">
-        <v>4.540954113006592</v>
+        <v>4.363183975219727</v>
       </c>
       <c r="I25" t="n">
-        <v>4.368941307067871</v>
+        <v>4.767256736755371</v>
       </c>
       <c r="J25" t="n">
-        <v>5.260632753372192</v>
+        <v>4.469672679901123</v>
       </c>
       <c r="K25" t="n">
-        <v>4.938814878463745</v>
+        <v>4.714828729629517</v>
       </c>
       <c r="L25" t="n">
-        <v>4.675998497009277</v>
+        <v>4.663415789604187</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.313587188720703</v>
+        <v>5.006572246551514</v>
       </c>
       <c r="C26" t="n">
-        <v>4.679394483566284</v>
+        <v>4.696465015411377</v>
       </c>
       <c r="D26" t="n">
-        <v>4.42750072479248</v>
+        <v>4.435843229293823</v>
       </c>
       <c r="E26" t="n">
-        <v>4.271409034729004</v>
+        <v>4.668141841888428</v>
       </c>
       <c r="F26" t="n">
-        <v>4.837449789047241</v>
+        <v>4.774013757705688</v>
       </c>
       <c r="G26" t="n">
-        <v>4.326266765594482</v>
+        <v>4.530529975891113</v>
       </c>
       <c r="H26" t="n">
-        <v>5.203922033309937</v>
+        <v>5.097891569137573</v>
       </c>
       <c r="I26" t="n">
-        <v>4.107840538024902</v>
+        <v>4.783954620361328</v>
       </c>
       <c r="J26" t="n">
-        <v>4.01552939414978</v>
+        <v>4.656224727630615</v>
       </c>
       <c r="K26" t="n">
-        <v>5.410016775131226</v>
+        <v>4.509317636489868</v>
       </c>
       <c r="L26" t="n">
-        <v>4.559291672706604</v>
+        <v>4.715895462036133</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.572625637054443</v>
+        <v>5.031887531280518</v>
       </c>
       <c r="C27" t="n">
-        <v>4.181124448776245</v>
+        <v>4.392456769943237</v>
       </c>
       <c r="D27" t="n">
-        <v>4.467895269393921</v>
+        <v>4.820167064666748</v>
       </c>
       <c r="E27" t="n">
-        <v>4.269769668579102</v>
+        <v>4.440985679626465</v>
       </c>
       <c r="F27" t="n">
-        <v>4.035063982009888</v>
+        <v>4.451434135437012</v>
       </c>
       <c r="G27" t="n">
-        <v>3.858128547668457</v>
+        <v>5.088509559631348</v>
       </c>
       <c r="H27" t="n">
-        <v>4.54468297958374</v>
+        <v>4.241851806640625</v>
       </c>
       <c r="I27" t="n">
-        <v>4.289387702941895</v>
+        <v>4.934761524200439</v>
       </c>
       <c r="J27" t="n">
-        <v>4.484878540039062</v>
+        <v>5.312238216400146</v>
       </c>
       <c r="K27" t="n">
-        <v>4.479860544204712</v>
+        <v>4.769059181213379</v>
       </c>
       <c r="L27" t="n">
-        <v>4.318341732025146</v>
+        <v>4.748335146903992</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.024550437927246</v>
+        <v>4.246455192565918</v>
       </c>
       <c r="C28" t="n">
-        <v>4.271871566772461</v>
+        <v>4.516998052597046</v>
       </c>
       <c r="D28" t="n">
-        <v>4.096894025802612</v>
+        <v>4.717931985855103</v>
       </c>
       <c r="E28" t="n">
-        <v>3.888473749160767</v>
+        <v>4.161059141159058</v>
       </c>
       <c r="F28" t="n">
-        <v>4.181145429611206</v>
+        <v>4.261862993240356</v>
       </c>
       <c r="G28" t="n">
-        <v>4.170663118362427</v>
+        <v>4.535943508148193</v>
       </c>
       <c r="H28" t="n">
-        <v>4.156224012374878</v>
+        <v>4.47014856338501</v>
       </c>
       <c r="I28" t="n">
-        <v>4.271811723709106</v>
+        <v>4.464102506637573</v>
       </c>
       <c r="J28" t="n">
-        <v>4.050703287124634</v>
+        <v>4.837962627410889</v>
       </c>
       <c r="K28" t="n">
-        <v>4.294990301132202</v>
+        <v>4.305666923522949</v>
       </c>
       <c r="L28" t="n">
-        <v>4.140732765197754</v>
+        <v>4.451813149452209</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>3.963197708129883</v>
+        <v>4.422461271286011</v>
       </c>
       <c r="C29" t="n">
-        <v>4.179155588150024</v>
+        <v>4.423325061798096</v>
       </c>
       <c r="D29" t="n">
-        <v>4.005542993545532</v>
+        <v>4.382225036621094</v>
       </c>
       <c r="E29" t="n">
-        <v>4.334483861923218</v>
+        <v>4.419509410858154</v>
       </c>
       <c r="F29" t="n">
-        <v>4.335409164428711</v>
+        <v>4.972592115402222</v>
       </c>
       <c r="G29" t="n">
-        <v>4.595945596694946</v>
+        <v>5.575460910797119</v>
       </c>
       <c r="H29" t="n">
-        <v>3.985638380050659</v>
+        <v>4.454147577285767</v>
       </c>
       <c r="I29" t="n">
-        <v>3.980648994445801</v>
+        <v>4.644380807876587</v>
       </c>
       <c r="J29" t="n">
-        <v>4.119651079177856</v>
+        <v>5.142116069793701</v>
       </c>
       <c r="K29" t="n">
-        <v>4.196320772171021</v>
+        <v>4.770371437072754</v>
       </c>
       <c r="L29" t="n">
-        <v>4.169599413871765</v>
+        <v>4.720658969879151</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.46790623664856</v>
+        <v>4.396079540252686</v>
       </c>
       <c r="C30" t="n">
-        <v>4.614015579223633</v>
+        <v>4.538041830062866</v>
       </c>
       <c r="D30" t="n">
-        <v>4.34321141242981</v>
+        <v>4.050917863845825</v>
       </c>
       <c r="E30" t="n">
-        <v>4.607027053833008</v>
+        <v>5.119860410690308</v>
       </c>
       <c r="F30" t="n">
-        <v>4.979117155075073</v>
+        <v>4.256618976593018</v>
       </c>
       <c r="G30" t="n">
-        <v>4.806053876876831</v>
+        <v>4.504301786422729</v>
       </c>
       <c r="H30" t="n">
-        <v>4.024138927459717</v>
+        <v>4.365233659744263</v>
       </c>
       <c r="I30" t="n">
-        <v>4.396094083786011</v>
+        <v>4.067822217941284</v>
       </c>
       <c r="J30" t="n">
-        <v>4.313312292098999</v>
+        <v>5.088063478469849</v>
       </c>
       <c r="K30" t="n">
-        <v>4.40556526184082</v>
+        <v>4.780839681625366</v>
       </c>
       <c r="L30" t="n">
-        <v>4.495644187927246</v>
+        <v>4.51677794456482</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>5.343619108200073</v>
+        <v>5.208121776580811</v>
       </c>
       <c r="C31" t="n">
-        <v>4.734204769134521</v>
+        <v>5.594857215881348</v>
       </c>
       <c r="D31" t="n">
-        <v>4.66839599609375</v>
+        <v>5.218542814254761</v>
       </c>
       <c r="E31" t="n">
-        <v>5.204528570175171</v>
+        <v>5.126333713531494</v>
       </c>
       <c r="F31" t="n">
-        <v>5.069851636886597</v>
+        <v>4.937175989151001</v>
       </c>
       <c r="G31" t="n">
-        <v>4.633967638015747</v>
+        <v>5.420941591262817</v>
       </c>
       <c r="H31" t="n">
-        <v>4.974100828170776</v>
+        <v>5.6500244140625</v>
       </c>
       <c r="I31" t="n">
-        <v>5.352535724639893</v>
+        <v>5.570383310317993</v>
       </c>
       <c r="J31" t="n">
-        <v>4.366893768310547</v>
+        <v>5.034327507019043</v>
       </c>
       <c r="K31" t="n">
-        <v>5.180019855499268</v>
+        <v>5.502638101577759</v>
       </c>
       <c r="L31" t="n">
-        <v>4.952811789512634</v>
+        <v>5.326334643363952</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.639942407608032</v>
+        <v>5.075583934783936</v>
       </c>
       <c r="C32" t="n">
-        <v>4.866852283477783</v>
+        <v>4.965906620025635</v>
       </c>
       <c r="D32" t="n">
-        <v>4.460401296615601</v>
+        <v>4.930122375488281</v>
       </c>
       <c r="E32" t="n">
-        <v>5.720661878585815</v>
+        <v>5.737032651901245</v>
       </c>
       <c r="F32" t="n">
-        <v>4.618020296096802</v>
+        <v>5.225080490112305</v>
       </c>
       <c r="G32" t="n">
-        <v>5.000040531158447</v>
+        <v>5.005583047866821</v>
       </c>
       <c r="H32" t="n">
-        <v>4.869860887527466</v>
+        <v>4.901053667068481</v>
       </c>
       <c r="I32" t="n">
-        <v>4.928711414337158</v>
+        <v>5.238539457321167</v>
       </c>
       <c r="J32" t="n">
-        <v>4.96262001991272</v>
+        <v>4.760640382766724</v>
       </c>
       <c r="K32" t="n">
-        <v>4.832960367202759</v>
+        <v>5.962642669677734</v>
       </c>
       <c r="L32" t="n">
-        <v>4.890007138252258</v>
+        <v>5.180218529701233</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>5.191001176834106</v>
+        <v>4.637343168258667</v>
       </c>
       <c r="C33" t="n">
-        <v>5.269840002059937</v>
+        <v>5.123007535934448</v>
       </c>
       <c r="D33" t="n">
-        <v>5.478805541992188</v>
+        <v>4.680306434631348</v>
       </c>
       <c r="E33" t="n">
-        <v>4.742487192153931</v>
+        <v>5.068708419799805</v>
       </c>
       <c r="F33" t="n">
-        <v>4.594320774078369</v>
+        <v>5.173683643341064</v>
       </c>
       <c r="G33" t="n">
-        <v>5.280104875564575</v>
+        <v>5.142598867416382</v>
       </c>
       <c r="H33" t="n">
-        <v>4.516994953155518</v>
+        <v>4.848710060119629</v>
       </c>
       <c r="I33" t="n">
-        <v>4.902102470397949</v>
+        <v>4.891279935836792</v>
       </c>
       <c r="J33" t="n">
-        <v>5.083065509796143</v>
+        <v>4.944687843322754</v>
       </c>
       <c r="K33" t="n">
-        <v>4.594328641891479</v>
+        <v>4.872503995895386</v>
       </c>
       <c r="L33" t="n">
-        <v>4.96530511379242</v>
+        <v>4.938282990455628</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.691102027893066</v>
+        <v>3.942920923233032</v>
       </c>
       <c r="C34" t="n">
-        <v>3.67414379119873</v>
+        <v>4.359036207199097</v>
       </c>
       <c r="D34" t="n">
-        <v>3.953433275222778</v>
+        <v>4.857209205627441</v>
       </c>
       <c r="E34" t="n">
-        <v>3.912549018859863</v>
+        <v>4.088811159133911</v>
       </c>
       <c r="F34" t="n">
-        <v>3.624767303466797</v>
+        <v>3.983678340911865</v>
       </c>
       <c r="G34" t="n">
-        <v>3.856680870056152</v>
+        <v>4.12068510055542</v>
       </c>
       <c r="H34" t="n">
-        <v>3.884118556976318</v>
+        <v>4.219912528991699</v>
       </c>
       <c r="I34" t="n">
-        <v>3.680133581161499</v>
+        <v>4.243014335632324</v>
       </c>
       <c r="J34" t="n">
-        <v>4.10903263092041</v>
+        <v>4.069735527038574</v>
       </c>
       <c r="K34" t="n">
-        <v>4.214294195175171</v>
+        <v>4.230911254882812</v>
       </c>
       <c r="L34" t="n">
-        <v>3.860025525093079</v>
+        <v>4.211591458320617</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>5.094115972518921</v>
+        <v>4.887852191925049</v>
       </c>
       <c r="C35" t="n">
-        <v>4.060201644897461</v>
+        <v>3.940160989761353</v>
       </c>
       <c r="D35" t="n">
-        <v>4.506530046463013</v>
+        <v>4.098531246185303</v>
       </c>
       <c r="E35" t="n">
-        <v>4.969978094100952</v>
+        <v>4.291639804840088</v>
       </c>
       <c r="F35" t="n">
-        <v>4.432283639907837</v>
+        <v>3.921998739242554</v>
       </c>
       <c r="G35" t="n">
-        <v>4.440738439559937</v>
+        <v>4.116833448410034</v>
       </c>
       <c r="H35" t="n">
-        <v>4.294617891311646</v>
+        <v>4.564915657043457</v>
       </c>
       <c r="I35" t="n">
-        <v>5.176397323608398</v>
+        <v>4.197246074676514</v>
       </c>
       <c r="J35" t="n">
-        <v>4.469248056411743</v>
+        <v>4.090022087097168</v>
       </c>
       <c r="K35" t="n">
-        <v>4.215323448181152</v>
+        <v>4.03740382194519</v>
       </c>
       <c r="L35" t="n">
-        <v>4.565943455696106</v>
+        <v>4.214660406112671</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>6.193536996841431</v>
+        <v>4.968735933303833</v>
       </c>
       <c r="C36" t="n">
-        <v>4.350212574005127</v>
+        <v>4.771008491516113</v>
       </c>
       <c r="D36" t="n">
-        <v>4.079899072647095</v>
+        <v>5.144410610198975</v>
       </c>
       <c r="E36" t="n">
-        <v>4.446491003036499</v>
+        <v>5.560702800750732</v>
       </c>
       <c r="F36" t="n">
-        <v>3.884409666061401</v>
+        <v>5.504908561706543</v>
       </c>
       <c r="G36" t="n">
-        <v>6.120349645614624</v>
+        <v>4.571610689163208</v>
       </c>
       <c r="H36" t="n">
-        <v>4.489882707595825</v>
+        <v>4.832958221435547</v>
       </c>
       <c r="I36" t="n">
-        <v>5.032966136932373</v>
+        <v>4.926856279373169</v>
       </c>
       <c r="J36" t="n">
-        <v>4.371686220169067</v>
+        <v>4.618574619293213</v>
       </c>
       <c r="K36" t="n">
-        <v>5.146230936050415</v>
+        <v>4.417738199234009</v>
       </c>
       <c r="L36" t="n">
-        <v>4.811566495895386</v>
+        <v>4.931750440597535</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.06535530090332</v>
+        <v>6.449616432189941</v>
       </c>
       <c r="C37" t="n">
-        <v>6.549678802490234</v>
+        <v>5.031916618347168</v>
       </c>
       <c r="D37" t="n">
-        <v>5.773900985717773</v>
+        <v>5.182397842407227</v>
       </c>
       <c r="E37" t="n">
-        <v>7.438755989074707</v>
+        <v>5.436589479446411</v>
       </c>
       <c r="F37" t="n">
-        <v>7.424542665481567</v>
+        <v>5.634414434432983</v>
       </c>
       <c r="G37" t="n">
-        <v>6.068936824798584</v>
+        <v>5.406755447387695</v>
       </c>
       <c r="H37" t="n">
-        <v>5.816895961761475</v>
+        <v>5.747733116149902</v>
       </c>
       <c r="I37" t="n">
-        <v>6.634345054626465</v>
+        <v>5.973528623580933</v>
       </c>
       <c r="J37" t="n">
-        <v>6.570342779159546</v>
+        <v>5.491987466812134</v>
       </c>
       <c r="K37" t="n">
-        <v>6.722516775131226</v>
+        <v>4.984514951705933</v>
       </c>
       <c r="L37" t="n">
-        <v>6.40652711391449</v>
+        <v>5.533945441246033</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.124077796936035</v>
+        <v>4.492812871932983</v>
       </c>
       <c r="C38" t="n">
-        <v>4.253227710723877</v>
+        <v>4.094195604324341</v>
       </c>
       <c r="D38" t="n">
-        <v>4.535005807876587</v>
+        <v>4.115782737731934</v>
       </c>
       <c r="E38" t="n">
-        <v>4.213369131088257</v>
+        <v>4.186559438705444</v>
       </c>
       <c r="F38" t="n">
-        <v>4.321512222290039</v>
+        <v>4.234971523284912</v>
       </c>
       <c r="G38" t="n">
-        <v>4.517016410827637</v>
+        <v>4.445531368255615</v>
       </c>
       <c r="H38" t="n">
-        <v>4.769137859344482</v>
+        <v>4.212137222290039</v>
       </c>
       <c r="I38" t="n">
-        <v>5.257983922958374</v>
+        <v>4.190345764160156</v>
       </c>
       <c r="J38" t="n">
-        <v>4.44756555557251</v>
+        <v>4.191383838653564</v>
       </c>
       <c r="K38" t="n">
-        <v>3.998634576797485</v>
+        <v>4.146248340606689</v>
       </c>
       <c r="L38" t="n">
-        <v>4.443753099441528</v>
+        <v>4.230996870994568</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>5.419046401977539</v>
+        <v>4.443883419036865</v>
       </c>
       <c r="C39" t="n">
-        <v>5.954043388366699</v>
+        <v>4.37889289855957</v>
       </c>
       <c r="D39" t="n">
-        <v>5.535247325897217</v>
+        <v>4.474887847900391</v>
       </c>
       <c r="E39" t="n">
-        <v>6.070674180984497</v>
+        <v>4.562334060668945</v>
       </c>
       <c r="F39" t="n">
-        <v>5.759009838104248</v>
+        <v>4.406888008117676</v>
       </c>
       <c r="G39" t="n">
-        <v>4.510057210922241</v>
+        <v>4.271221399307251</v>
       </c>
       <c r="H39" t="n">
-        <v>4.324548959732056</v>
+        <v>4.412274837493896</v>
       </c>
       <c r="I39" t="n">
-        <v>5.045303344726562</v>
+        <v>4.396024227142334</v>
       </c>
       <c r="J39" t="n">
-        <v>4.362676620483398</v>
+        <v>5.366805553436279</v>
       </c>
       <c r="K39" t="n">
-        <v>3.971415042877197</v>
+        <v>4.561766862869263</v>
       </c>
       <c r="L39" t="n">
-        <v>5.095202231407166</v>
+        <v>4.527497911453247</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>6.654849529266357</v>
+        <v>5.761338949203491</v>
       </c>
       <c r="C40" t="n">
-        <v>4.656913757324219</v>
+        <v>4.894062280654907</v>
       </c>
       <c r="D40" t="n">
-        <v>4.44494891166687</v>
+        <v>4.898809194564819</v>
       </c>
       <c r="E40" t="n">
-        <v>4.699315071105957</v>
+        <v>4.880102157592773</v>
       </c>
       <c r="F40" t="n">
-        <v>4.472412109375</v>
+        <v>4.819372892379761</v>
       </c>
       <c r="G40" t="n">
-        <v>4.65240740776062</v>
+        <v>5.900101900100708</v>
       </c>
       <c r="H40" t="n">
-        <v>4.722241878509521</v>
+        <v>5.208674669265747</v>
       </c>
       <c r="I40" t="n">
-        <v>5.341628074645996</v>
+        <v>5.839352130889893</v>
       </c>
       <c r="J40" t="n">
-        <v>4.572109460830688</v>
+        <v>4.749810218811035</v>
       </c>
       <c r="K40" t="n">
-        <v>5.074995756149292</v>
+        <v>4.772972106933594</v>
       </c>
       <c r="L40" t="n">
-        <v>4.929182195663453</v>
+        <v>5.172459650039673</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.133856058120728</v>
+        <v>4.572767019271851</v>
       </c>
       <c r="C41" t="n">
-        <v>4.477650165557861</v>
+        <v>4.262234210968018</v>
       </c>
       <c r="D41" t="n">
-        <v>4.55893874168396</v>
+        <v>4.298143625259399</v>
       </c>
       <c r="E41" t="n">
-        <v>4.810981512069702</v>
+        <v>4.415113687515259</v>
       </c>
       <c r="F41" t="n">
-        <v>4.801554441452026</v>
+        <v>4.904548645019531</v>
       </c>
       <c r="G41" t="n">
-        <v>4.481353044509888</v>
+        <v>4.400851964950562</v>
       </c>
       <c r="H41" t="n">
-        <v>4.349719524383545</v>
+        <v>4.569049596786499</v>
       </c>
       <c r="I41" t="n">
-        <v>4.075422763824463</v>
+        <v>4.628490686416626</v>
       </c>
       <c r="J41" t="n">
-        <v>4.638440370559692</v>
+        <v>4.475012302398682</v>
       </c>
       <c r="K41" t="n">
-        <v>4.007602214813232</v>
+        <v>5.484000205993652</v>
       </c>
       <c r="L41" t="n">
-        <v>4.433551883697509</v>
+        <v>4.601021194458008</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.756161212921143</v>
+        <v>5.122678756713867</v>
       </c>
       <c r="C42" t="n">
-        <v>5.088300704956055</v>
+        <v>5.18986964225769</v>
       </c>
       <c r="D42" t="n">
-        <v>4.845447063446045</v>
+        <v>5.895015478134155</v>
       </c>
       <c r="E42" t="n">
-        <v>5.030503273010254</v>
+        <v>5.133946895599365</v>
       </c>
       <c r="F42" t="n">
-        <v>5.180098533630371</v>
+        <v>4.831554889678955</v>
       </c>
       <c r="G42" t="n">
-        <v>4.853995323181152</v>
+        <v>5.117898941040039</v>
       </c>
       <c r="H42" t="n">
-        <v>5.368605613708496</v>
+        <v>4.981305122375488</v>
       </c>
       <c r="I42" t="n">
-        <v>4.603374481201172</v>
+        <v>4.820204496383667</v>
       </c>
       <c r="J42" t="n">
-        <v>4.785104990005493</v>
+        <v>5.427982091903687</v>
       </c>
       <c r="K42" t="n">
-        <v>5.77898907661438</v>
+        <v>5.465017795562744</v>
       </c>
       <c r="L42" t="n">
-        <v>5.029058027267456</v>
+        <v>5.198547410964966</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.581844806671143</v>
+        <v>5.222686529159546</v>
       </c>
       <c r="C43" t="n">
-        <v>4.852163076400757</v>
+        <v>5.72950553894043</v>
       </c>
       <c r="D43" t="n">
-        <v>5.375889539718628</v>
+        <v>4.644584894180298</v>
       </c>
       <c r="E43" t="n">
-        <v>5.59891414642334</v>
+        <v>5.37798285484314</v>
       </c>
       <c r="F43" t="n">
-        <v>5.244213342666626</v>
+        <v>5.113132953643799</v>
       </c>
       <c r="G43" t="n">
-        <v>5.98634672164917</v>
+        <v>4.84592342376709</v>
       </c>
       <c r="H43" t="n">
-        <v>6.298223972320557</v>
+        <v>6.521930694580078</v>
       </c>
       <c r="I43" t="n">
-        <v>4.626619577407837</v>
+        <v>4.947816371917725</v>
       </c>
       <c r="J43" t="n">
-        <v>5.374370098114014</v>
+        <v>5.026675224304199</v>
       </c>
       <c r="K43" t="n">
-        <v>4.917041301727295</v>
+        <v>4.787521600723267</v>
       </c>
       <c r="L43" t="n">
-        <v>5.285562658309937</v>
+        <v>5.221776008605957</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.055683851242065</v>
+        <v>4.374845266342163</v>
       </c>
       <c r="C44" t="n">
-        <v>4.199163675308228</v>
+        <v>5.080311298370361</v>
       </c>
       <c r="D44" t="n">
-        <v>4.573344945907593</v>
+        <v>4.756890535354614</v>
       </c>
       <c r="E44" t="n">
-        <v>4.175399780273438</v>
+        <v>4.384001970291138</v>
       </c>
       <c r="F44" t="n">
-        <v>4.345441102981567</v>
+        <v>5.146854877471924</v>
       </c>
       <c r="G44" t="n">
-        <v>3.879631519317627</v>
+        <v>4.690234184265137</v>
       </c>
       <c r="H44" t="n">
-        <v>4.158917427062988</v>
+        <v>5.424226522445679</v>
       </c>
       <c r="I44" t="n">
-        <v>4.336468935012817</v>
+        <v>4.980294227600098</v>
       </c>
       <c r="J44" t="n">
-        <v>4.253710031509399</v>
+        <v>4.70265793800354</v>
       </c>
       <c r="K44" t="n">
-        <v>4.085610151290894</v>
+        <v>4.598147630691528</v>
       </c>
       <c r="L44" t="n">
-        <v>4.206337141990661</v>
+        <v>4.813846445083618</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>3.818264245986938</v>
+        <v>4.216776371002197</v>
       </c>
       <c r="C45" t="n">
-        <v>4.139269351959229</v>
+        <v>3.776748895645142</v>
       </c>
       <c r="D45" t="n">
-        <v>3.909347057342529</v>
+        <v>4.211899042129517</v>
       </c>
       <c r="E45" t="n">
-        <v>4.255466461181641</v>
+        <v>4.244788408279419</v>
       </c>
       <c r="F45" t="n">
-        <v>3.925295114517212</v>
+        <v>4.612315654754639</v>
       </c>
       <c r="G45" t="n">
-        <v>4.041495561599731</v>
+        <v>4.736870050430298</v>
       </c>
       <c r="H45" t="n">
-        <v>4.072943925857544</v>
+        <v>4.396371126174927</v>
       </c>
       <c r="I45" t="n">
-        <v>3.931265592575073</v>
+        <v>4.144633054733276</v>
       </c>
       <c r="J45" t="n">
-        <v>4.3282630443573</v>
+        <v>4.479353666305542</v>
       </c>
       <c r="K45" t="n">
-        <v>3.692895650863647</v>
+        <v>4.534569501876831</v>
       </c>
       <c r="L45" t="n">
-        <v>4.011450600624085</v>
+        <v>4.335432577133179</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.355159044265747</v>
+        <v>4.64124870300293</v>
       </c>
       <c r="C46" t="n">
-        <v>4.927931785583496</v>
+        <v>4.653562068939209</v>
       </c>
       <c r="D46" t="n">
-        <v>4.786492347717285</v>
+        <v>4.866885423660278</v>
       </c>
       <c r="E46" t="n">
-        <v>4.748953342437744</v>
+        <v>5.134837865829468</v>
       </c>
       <c r="F46" t="n">
-        <v>4.169882297515869</v>
+        <v>4.336185932159424</v>
       </c>
       <c r="G46" t="n">
-        <v>4.686609268188477</v>
+        <v>4.680615663528442</v>
       </c>
       <c r="H46" t="n">
-        <v>4.67660927772522</v>
+        <v>4.389987230300903</v>
       </c>
       <c r="I46" t="n">
-        <v>4.751054286956787</v>
+        <v>4.806177616119385</v>
       </c>
       <c r="J46" t="n">
-        <v>4.469154596328735</v>
+        <v>4.988463163375854</v>
       </c>
       <c r="K46" t="n">
-        <v>4.472230434417725</v>
+        <v>4.441924810409546</v>
       </c>
       <c r="L46" t="n">
-        <v>4.604407668113708</v>
+        <v>4.693988847732544</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>5.656378984451294</v>
+        <v>4.425206899642944</v>
       </c>
       <c r="C47" t="n">
-        <v>3.758968114852905</v>
+        <v>3.901286125183105</v>
       </c>
       <c r="D47" t="n">
-        <v>3.746482133865356</v>
+        <v>4.72234845161438</v>
       </c>
       <c r="E47" t="n">
-        <v>3.565412998199463</v>
+        <v>4.250842571258545</v>
       </c>
       <c r="F47" t="n">
-        <v>3.653205633163452</v>
+        <v>3.943907260894775</v>
       </c>
       <c r="G47" t="n">
-        <v>4.037636041641235</v>
+        <v>4.100566148757935</v>
       </c>
       <c r="H47" t="n">
-        <v>4.016569852828979</v>
+        <v>4.700515031814575</v>
       </c>
       <c r="I47" t="n">
-        <v>4.474885940551758</v>
+        <v>4.186841011047363</v>
       </c>
       <c r="J47" t="n">
-        <v>4.015560388565063</v>
+        <v>4.360487222671509</v>
       </c>
       <c r="K47" t="n">
-        <v>3.642522573471069</v>
+        <v>4.444490909576416</v>
       </c>
       <c r="L47" t="n">
-        <v>4.056762266159057</v>
+        <v>4.303649163246154</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.547164440155029</v>
+        <v>5.008424282073975</v>
       </c>
       <c r="C48" t="n">
-        <v>4.049456834793091</v>
+        <v>4.931118965148926</v>
       </c>
       <c r="D48" t="n">
-        <v>4.563127756118774</v>
+        <v>4.970480680465698</v>
       </c>
       <c r="E48" t="n">
-        <v>4.822459697723389</v>
+        <v>4.879226684570312</v>
       </c>
       <c r="F48" t="n">
-        <v>4.514762878417969</v>
+        <v>5.092970609664917</v>
       </c>
       <c r="G48" t="n">
-        <v>4.624981880187988</v>
+        <v>5.024467706680298</v>
       </c>
       <c r="H48" t="n">
-        <v>4.265893220901489</v>
+        <v>6.324886322021484</v>
       </c>
       <c r="I48" t="n">
-        <v>4.376613855361938</v>
+        <v>4.846641540527344</v>
       </c>
       <c r="J48" t="n">
-        <v>4.143728017807007</v>
+        <v>4.899502038955688</v>
       </c>
       <c r="K48" t="n">
-        <v>5.169558525085449</v>
+        <v>5.12678599357605</v>
       </c>
       <c r="L48" t="n">
-        <v>4.507774710655212</v>
+        <v>5.110450482368469</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.02851128578186</v>
+        <v>4.711111783981323</v>
       </c>
       <c r="C49" t="n">
-        <v>3.936285734176636</v>
+        <v>4.904631853103638</v>
       </c>
       <c r="D49" t="n">
-        <v>4.66740894317627</v>
+        <v>5.439098596572876</v>
       </c>
       <c r="E49" t="n">
-        <v>5.257132291793823</v>
+        <v>5.009392738342285</v>
       </c>
       <c r="F49" t="n">
-        <v>4.60094165802002</v>
+        <v>4.971062660217285</v>
       </c>
       <c r="G49" t="n">
-        <v>4.386734247207642</v>
+        <v>5.628426074981689</v>
       </c>
       <c r="H49" t="n">
-        <v>4.819921255111694</v>
+        <v>5.248048543930054</v>
       </c>
       <c r="I49" t="n">
-        <v>4.560936450958252</v>
+        <v>5.056540250778198</v>
       </c>
       <c r="J49" t="n">
-        <v>5.562132835388184</v>
+        <v>5.055378198623657</v>
       </c>
       <c r="K49" t="n">
-        <v>5.563621044158936</v>
+        <v>4.974527835845947</v>
       </c>
       <c r="L49" t="n">
-        <v>4.738362574577332</v>
+        <v>5.099821853637695</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.868677139282227</v>
+        <v>3.938674449920654</v>
       </c>
       <c r="C50" t="n">
-        <v>4.647404432296753</v>
+        <v>4.492889881134033</v>
       </c>
       <c r="D50" t="n">
-        <v>4.261010885238647</v>
+        <v>4.579718828201294</v>
       </c>
       <c r="E50" t="n">
-        <v>4.591350078582764</v>
+        <v>4.750608682632446</v>
       </c>
       <c r="F50" t="n">
-        <v>4.349272489547729</v>
+        <v>4.609253406524658</v>
       </c>
       <c r="G50" t="n">
-        <v>4.270621538162231</v>
+        <v>4.314056396484375</v>
       </c>
       <c r="H50" t="n">
-        <v>4.173559188842773</v>
+        <v>4.755161762237549</v>
       </c>
       <c r="I50" t="n">
-        <v>4.361260652542114</v>
+        <v>4.274359226226807</v>
       </c>
       <c r="J50" t="n">
-        <v>4.499087810516357</v>
+        <v>4.398017406463623</v>
       </c>
       <c r="K50" t="n">
-        <v>4.95500636100769</v>
+        <v>4.322837352752686</v>
       </c>
       <c r="L50" t="n">
-        <v>4.397725057601929</v>
+        <v>4.443557739257812</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.854207992553711</v>
+        <v>4.855092525482178</v>
       </c>
       <c r="C51" t="n">
-        <v>4.764517545700073</v>
+        <v>4.962261438369751</v>
       </c>
       <c r="D51" t="n">
-        <v>4.496843814849854</v>
+        <v>4.870866060256958</v>
       </c>
       <c r="E51" t="n">
-        <v>4.650439262390137</v>
+        <v>5.158874034881592</v>
       </c>
       <c r="F51" t="n">
-        <v>4.597071886062622</v>
+        <v>4.706320524215698</v>
       </c>
       <c r="G51" t="n">
-        <v>4.215652942657471</v>
+        <v>5.164625883102417</v>
       </c>
       <c r="H51" t="n">
-        <v>4.002820730209351</v>
+        <v>4.671484708786011</v>
       </c>
       <c r="I51" t="n">
-        <v>4.737565994262695</v>
+        <v>4.273958444595337</v>
       </c>
       <c r="J51" t="n">
-        <v>4.435758113861084</v>
+        <v>4.452500104904175</v>
       </c>
       <c r="K51" t="n">
-        <v>4.290606260299683</v>
+        <v>4.29435920715332</v>
       </c>
       <c r="L51" t="n">
-        <v>4.504548454284668</v>
+        <v>4.741034293174744</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.682174344062805</v>
+        <v>4.789972233772278</v>
       </c>
       <c r="C52" t="n">
-        <v>4.611092004776001</v>
+        <v>4.727252769470215</v>
       </c>
       <c r="D52" t="n">
-        <v>4.622644815444946</v>
+        <v>4.744769988059997</v>
       </c>
       <c r="E52" t="n">
-        <v>4.740476956367493</v>
+        <v>4.770836482048034</v>
       </c>
       <c r="F52" t="n">
-        <v>4.57951434135437</v>
+        <v>4.715227003097534</v>
       </c>
       <c r="G52" t="n">
-        <v>4.669910683631897</v>
+        <v>4.821874237060547</v>
       </c>
       <c r="H52" t="n">
-        <v>4.640848460197449</v>
+        <v>4.871653723716736</v>
       </c>
       <c r="I52" t="n">
-        <v>4.716432480812073</v>
+        <v>4.739594202041626</v>
       </c>
       <c r="J52" t="n">
-        <v>4.632320098876953</v>
+        <v>4.765604906082153</v>
       </c>
       <c r="K52" t="n">
-        <v>4.635415120124817</v>
+        <v>4.737232022285461</v>
       </c>
       <c r="L52" t="n">
-        <v>4.653082930564881</v>
+        <v>4.768401756763458</v>
       </c>
     </row>
   </sheetData>
